--- a/public/test_labs.xlsx
+++ b/public/test_labs.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H217"/>
+  <dimension ref="A1:H285"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5959,9 +5959,1777 @@
         <v>49</v>
       </c>
     </row>
+    <row r="218">
+      <c r="A218">
+        <v>3</v>
+      </c>
+      <c r="B218" s="1">
+        <v>44562.041666666664</v>
+      </c>
+      <c r="C218" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D218" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E218" t="str">
+        <v>74,1</v>
+      </c>
+      <c r="F218" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G218" t="str">
+        <v>w</v>
+      </c>
+      <c r="H218">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>3</v>
+      </c>
+      <c r="B219" s="1">
+        <v>45292.041666666664</v>
+      </c>
+      <c r="C219" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D219" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E219" t="str">
+        <v>43,1</v>
+      </c>
+      <c r="F219" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G219" t="str">
+        <v>w</v>
+      </c>
+      <c r="H219">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>4</v>
+      </c>
+      <c r="B220" s="1">
+        <v>44562.041666666664</v>
+      </c>
+      <c r="C220" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D220" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E220" t="str">
+        <v>91,7</v>
+      </c>
+      <c r="F220" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G220" t="str">
+        <v>m</v>
+      </c>
+      <c r="H220">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>4</v>
+      </c>
+      <c r="B221" s="1">
+        <v>44652.083333333336</v>
+      </c>
+      <c r="C221" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D221" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E221" t="str">
+        <v>86,5</v>
+      </c>
+      <c r="F221" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G221" t="str">
+        <v>m</v>
+      </c>
+      <c r="H221">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>4</v>
+      </c>
+      <c r="B222" s="1">
+        <v>44742.083333333336</v>
+      </c>
+      <c r="C222" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D222" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E222" t="str">
+        <v>81,8</v>
+      </c>
+      <c r="F222" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G222" t="str">
+        <v>m</v>
+      </c>
+      <c r="H222">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>4</v>
+      </c>
+      <c r="B223" s="1">
+        <v>44832.083333333336</v>
+      </c>
+      <c r="C223" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D223" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E223" t="str">
+        <v>79,5</v>
+      </c>
+      <c r="F223" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G223" t="str">
+        <v>m</v>
+      </c>
+      <c r="H223">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>4</v>
+      </c>
+      <c r="B224" s="1">
+        <v>44922.041666666664</v>
+      </c>
+      <c r="C224" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D224" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E224" t="str">
+        <v>73,2</v>
+      </c>
+      <c r="F224" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G224" t="str">
+        <v>m</v>
+      </c>
+      <c r="H224">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>4</v>
+      </c>
+      <c r="B225" s="1">
+        <v>45012.083333333336</v>
+      </c>
+      <c r="C225" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D225" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E225" t="str">
+        <v>69,7</v>
+      </c>
+      <c r="F225" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G225" t="str">
+        <v>m</v>
+      </c>
+      <c r="H225">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>4</v>
+      </c>
+      <c r="B226" s="1">
+        <v>45102.083333333336</v>
+      </c>
+      <c r="C226" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D226" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E226" t="str">
+        <v>66,5</v>
+      </c>
+      <c r="F226" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G226" t="str">
+        <v>m</v>
+      </c>
+      <c r="H226">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>4</v>
+      </c>
+      <c r="B227" s="1">
+        <v>45192.083333333336</v>
+      </c>
+      <c r="C227" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D227" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E227" t="str">
+        <v>63,2</v>
+      </c>
+      <c r="F227" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G227" t="str">
+        <v>m</v>
+      </c>
+      <c r="H227">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>6</v>
+      </c>
+      <c r="B228" s="1">
+        <v>44571.041666666664</v>
+      </c>
+      <c r="C228" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D228" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E228" t="str">
+        <v>65,5</v>
+      </c>
+      <c r="F228" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G228" t="str">
+        <v>m</v>
+      </c>
+      <c r="H228">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>6</v>
+      </c>
+      <c r="B229" s="1">
+        <v>44661.083333333336</v>
+      </c>
+      <c r="C229" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D229" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E229" t="str">
+        <v>62,3</v>
+      </c>
+      <c r="F229" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G229" t="str">
+        <v>m</v>
+      </c>
+      <c r="H229">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>6</v>
+      </c>
+      <c r="B230" s="1">
+        <v>44752.083333333336</v>
+      </c>
+      <c r="C230" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D230" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E230" t="str">
+        <v>59,5</v>
+      </c>
+      <c r="F230" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G230" t="str">
+        <v>m</v>
+      </c>
+      <c r="H230">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>6</v>
+      </c>
+      <c r="B231" s="1">
+        <v>44809.083333333336</v>
+      </c>
+      <c r="C231" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D231" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E231" t="str">
+        <v>59,1</v>
+      </c>
+      <c r="F231" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G231" t="str">
+        <v>m</v>
+      </c>
+      <c r="H231">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>6</v>
+      </c>
+      <c r="B232" s="1">
+        <v>44812.083333333336</v>
+      </c>
+      <c r="C232" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D232" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E232" t="str">
+        <v>22,6</v>
+      </c>
+      <c r="F232" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G232" t="str">
+        <v>m</v>
+      </c>
+      <c r="H232">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>6</v>
+      </c>
+      <c r="B233" s="1">
+        <v>44820.083333333336</v>
+      </c>
+      <c r="C233" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D233" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E233" t="str">
+        <v>35,2</v>
+      </c>
+      <c r="F233" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G233" t="str">
+        <v>m</v>
+      </c>
+      <c r="H233">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>6</v>
+      </c>
+      <c r="B234" s="1">
+        <v>44832.083333333336</v>
+      </c>
+      <c r="C234" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D234" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E234" t="str">
+        <v>49,8</v>
+      </c>
+      <c r="F234" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G234" t="str">
+        <v>m</v>
+      </c>
+      <c r="H234">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>6</v>
+      </c>
+      <c r="B235" s="1">
+        <v>44905.041666666664</v>
+      </c>
+      <c r="C235" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D235" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E235" t="str">
+        <v>56,5</v>
+      </c>
+      <c r="F235" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G235" t="str">
+        <v>m</v>
+      </c>
+      <c r="H235">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>6</v>
+      </c>
+      <c r="B236" s="1">
+        <v>44995.041666666664</v>
+      </c>
+      <c r="C236" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D236" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E236" t="str">
+        <v>54,1</v>
+      </c>
+      <c r="F236" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G236" t="str">
+        <v>m</v>
+      </c>
+      <c r="H236">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>6</v>
+      </c>
+      <c r="B237" s="1">
+        <v>45087.083333333336</v>
+      </c>
+      <c r="C237" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D237" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E237" t="str">
+        <v>51,8</v>
+      </c>
+      <c r="F237" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G237" t="str">
+        <v>m</v>
+      </c>
+      <c r="H237">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>6</v>
+      </c>
+      <c r="B238" s="1">
+        <v>45179.083333333336</v>
+      </c>
+      <c r="C238" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D238" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E238" t="str">
+        <v>49,5</v>
+      </c>
+      <c r="F238" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G238" t="str">
+        <v>m</v>
+      </c>
+      <c r="H238">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>7</v>
+      </c>
+      <c r="B239" s="1">
+        <v>44197.041666666664</v>
+      </c>
+      <c r="C239" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D239" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E239" t="str">
+        <v>80,0</v>
+      </c>
+      <c r="F239" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G239" t="str">
+        <v>m</v>
+      </c>
+      <c r="H239">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>7</v>
+      </c>
+      <c r="B240" s="1">
+        <v>44256.041666666664</v>
+      </c>
+      <c r="C240" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D240" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E240" t="str">
+        <v>75,4</v>
+      </c>
+      <c r="F240" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G240" t="str">
+        <v>m</v>
+      </c>
+      <c r="H240">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>7</v>
+      </c>
+      <c r="B241" s="1">
+        <v>44348.083333333336</v>
+      </c>
+      <c r="C241" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D241" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E241" t="str">
+        <v>71,3</v>
+      </c>
+      <c r="F241" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G241" t="str">
+        <v>m</v>
+      </c>
+      <c r="H241">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>7</v>
+      </c>
+      <c r="B242" s="1">
+        <v>44350.083333333336</v>
+      </c>
+      <c r="C242" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D242" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E242" t="str">
+        <v>47,3</v>
+      </c>
+      <c r="F242" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G242" t="str">
+        <v>m</v>
+      </c>
+      <c r="H242">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>7</v>
+      </c>
+      <c r="B243" s="1">
+        <v>44359.083333333336</v>
+      </c>
+      <c r="C243" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D243" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E243" t="str">
+        <v>64,3</v>
+      </c>
+      <c r="F243" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G243" t="str">
+        <v>m</v>
+      </c>
+      <c r="H243">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>7</v>
+      </c>
+      <c r="B244" s="1">
+        <v>44440.083333333336</v>
+      </c>
+      <c r="C244" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D244" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E244" t="str">
+        <v>70,9</v>
+      </c>
+      <c r="F244" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G244" t="str">
+        <v>m</v>
+      </c>
+      <c r="H244">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>7</v>
+      </c>
+      <c r="B245" s="1">
+        <v>44562.041666666664</v>
+      </c>
+      <c r="C245" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D245" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E245" t="str">
+        <v>67,2</v>
+      </c>
+      <c r="F245" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G245" t="str">
+        <v>m</v>
+      </c>
+      <c r="H245">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>7</v>
+      </c>
+      <c r="B246" s="1">
+        <v>44565.041666666664</v>
+      </c>
+      <c r="C246" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D246" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E246" t="str">
+        <v>28,5</v>
+      </c>
+      <c r="F246" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G246" t="str">
+        <v>m</v>
+      </c>
+      <c r="H246">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>7</v>
+      </c>
+      <c r="B247" s="1">
+        <v>44581.041666666664</v>
+      </c>
+      <c r="C247" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D247" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E247" t="str">
+        <v>55,4</v>
+      </c>
+      <c r="F247" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G247" t="str">
+        <v>m</v>
+      </c>
+      <c r="H247">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>7</v>
+      </c>
+      <c r="B248" s="1">
+        <v>44713.083333333336</v>
+      </c>
+      <c r="C248" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D248" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E248" t="str">
+        <v>63,9</v>
+      </c>
+      <c r="F248" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G248" t="str">
+        <v>m</v>
+      </c>
+      <c r="H248">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>7</v>
+      </c>
+      <c r="B249" s="1">
+        <v>44835.083333333336</v>
+      </c>
+      <c r="C249" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D249" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E249" t="str">
+        <v>60,4</v>
+      </c>
+      <c r="F249" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G249" t="str">
+        <v>m</v>
+      </c>
+      <c r="H249">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>7</v>
+      </c>
+      <c r="B250" s="1">
+        <v>44837.083333333336</v>
+      </c>
+      <c r="C250" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D250" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E250" t="str">
+        <v>14,1</v>
+      </c>
+      <c r="F250" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G250" t="str">
+        <v>m</v>
+      </c>
+      <c r="H250">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>7</v>
+      </c>
+      <c r="B251" s="1">
+        <v>44852.083333333336</v>
+      </c>
+      <c r="C251" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D251" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E251" t="str">
+        <v>34,4</v>
+      </c>
+      <c r="F251" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G251" t="str">
+        <v>m</v>
+      </c>
+      <c r="H251">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>7</v>
+      </c>
+      <c r="B252" s="1">
+        <v>44927.041666666664</v>
+      </c>
+      <c r="C252" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D252" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E252" t="str">
+        <v>55,1</v>
+      </c>
+      <c r="F252" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G252" t="str">
+        <v>m</v>
+      </c>
+      <c r="H252">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>7</v>
+      </c>
+      <c r="B253" s="1">
+        <v>45078.083333333336</v>
+      </c>
+      <c r="C253" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D253" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E253" t="str">
+        <v>52,7</v>
+      </c>
+      <c r="F253" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G253" t="str">
+        <v>m</v>
+      </c>
+      <c r="H253">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>8</v>
+      </c>
+      <c r="B254" s="1">
+        <v>43862.041666666664</v>
+      </c>
+      <c r="C254" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D254" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E254" t="str">
+        <v>69,9</v>
+      </c>
+      <c r="F254" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G254" t="str">
+        <v>w</v>
+      </c>
+      <c r="H254">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>8</v>
+      </c>
+      <c r="B255" s="1">
+        <v>44044.083333333336</v>
+      </c>
+      <c r="C255" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D255" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E255" t="str">
+        <v>68,2</v>
+      </c>
+      <c r="F255" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G255" t="str">
+        <v>w</v>
+      </c>
+      <c r="H255">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>8</v>
+      </c>
+      <c r="B256" s="1">
+        <v>44228.041666666664</v>
+      </c>
+      <c r="C256" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D256" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E256" t="str">
+        <v>68,6</v>
+      </c>
+      <c r="F256" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G256" t="str">
+        <v>w</v>
+      </c>
+      <c r="H256">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>8</v>
+      </c>
+      <c r="B257" s="1">
+        <v>44409.083333333336</v>
+      </c>
+      <c r="C257" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D257" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E257" t="str">
+        <v>66,9</v>
+      </c>
+      <c r="F257" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G257" t="str">
+        <v>w</v>
+      </c>
+      <c r="H257">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>8</v>
+      </c>
+      <c r="B258" s="1">
+        <v>44593.041666666664</v>
+      </c>
+      <c r="C258" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D258" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E258" t="str">
+        <v>65,7</v>
+      </c>
+      <c r="F258" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G258" t="str">
+        <v>w</v>
+      </c>
+      <c r="H258">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>8</v>
+      </c>
+      <c r="B259" s="1">
+        <v>44774.083333333336</v>
+      </c>
+      <c r="C259" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D259" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E259" t="str">
+        <v>67,3</v>
+      </c>
+      <c r="F259" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G259" t="str">
+        <v>w</v>
+      </c>
+      <c r="H259">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>8</v>
+      </c>
+      <c r="B260" s="1">
+        <v>44958.041666666664</v>
+      </c>
+      <c r="C260" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D260" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E260" t="str">
+        <v>66,1</v>
+      </c>
+      <c r="F260" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G260" t="str">
+        <v>w</v>
+      </c>
+      <c r="H260">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>8</v>
+      </c>
+      <c r="B261" s="1">
+        <v>45139.083333333336</v>
+      </c>
+      <c r="C261" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D261" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E261" t="str">
+        <v>64,5</v>
+      </c>
+      <c r="F261" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G261" t="str">
+        <v>w</v>
+      </c>
+      <c r="H261">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>8</v>
+      </c>
+      <c r="B262" s="1">
+        <v>45323.041666666664</v>
+      </c>
+      <c r="C262" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D262" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E262" t="str">
+        <v>64,9</v>
+      </c>
+      <c r="F262" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G262" t="str">
+        <v>w</v>
+      </c>
+      <c r="H262">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>8</v>
+      </c>
+      <c r="B263" s="1">
+        <v>45505.083333333336</v>
+      </c>
+      <c r="C263" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D263" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E263" t="str">
+        <v>63,4</v>
+      </c>
+      <c r="F263" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G263" t="str">
+        <v>w</v>
+      </c>
+      <c r="H263">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>8</v>
+      </c>
+      <c r="B264" s="1">
+        <v>45689.041666666664</v>
+      </c>
+      <c r="C264" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D264" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E264" t="str">
+        <v>63,7</v>
+      </c>
+      <c r="F264" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G264" t="str">
+        <v>w</v>
+      </c>
+      <c r="H264">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>8</v>
+      </c>
+      <c r="B265" s="1">
+        <v>45870.083333333336</v>
+      </c>
+      <c r="C265" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D265" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E265" t="str">
+        <v>62,2</v>
+      </c>
+      <c r="F265" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G265" t="str">
+        <v>w</v>
+      </c>
+      <c r="H265">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>9</v>
+      </c>
+      <c r="B266" s="1">
+        <v>43497.041666666664</v>
+      </c>
+      <c r="C266" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D266" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E266" t="str">
+        <v>68,2</v>
+      </c>
+      <c r="F266" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G266" t="str">
+        <v>w</v>
+      </c>
+      <c r="H266">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>9</v>
+      </c>
+      <c r="B267" s="1">
+        <v>43739.083333333336</v>
+      </c>
+      <c r="C267" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D267" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E267" t="str">
+        <v>61,4</v>
+      </c>
+      <c r="F267" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G267" t="str">
+        <v>w</v>
+      </c>
+      <c r="H267">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>9</v>
+      </c>
+      <c r="B268" s="1">
+        <v>43983.083333333336</v>
+      </c>
+      <c r="C268" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D268" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E268" t="str">
+        <v>56,0</v>
+      </c>
+      <c r="F268" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G268" t="str">
+        <v>w</v>
+      </c>
+      <c r="H268">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>9</v>
+      </c>
+      <c r="B269" s="1">
+        <v>44228.041666666664</v>
+      </c>
+      <c r="C269" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D269" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E269" t="str">
+        <v>50,0</v>
+      </c>
+      <c r="F269" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G269" t="str">
+        <v>w</v>
+      </c>
+      <c r="H269">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>9</v>
+      </c>
+      <c r="B270" s="1">
+        <v>44470.083333333336</v>
+      </c>
+      <c r="C270" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D270" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E270" t="str">
+        <v>43,4</v>
+      </c>
+      <c r="F270" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G270" t="str">
+        <v>w</v>
+      </c>
+      <c r="H270">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>9</v>
+      </c>
+      <c r="B271" s="1">
+        <v>44713.083333333336</v>
+      </c>
+      <c r="C271" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D271" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E271" t="str">
+        <v>37,9</v>
+      </c>
+      <c r="F271" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G271" t="str">
+        <v>w</v>
+      </c>
+      <c r="H271">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>9</v>
+      </c>
+      <c r="B272" s="1">
+        <v>44958.041666666664</v>
+      </c>
+      <c r="C272" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D272" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E272" t="str">
+        <v>33,0</v>
+      </c>
+      <c r="F272" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G272" t="str">
+        <v>w</v>
+      </c>
+      <c r="H272">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>9</v>
+      </c>
+      <c r="B273" s="1">
+        <v>45200.083333333336</v>
+      </c>
+      <c r="C273" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D273" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E273" t="str">
+        <v>29,2</v>
+      </c>
+      <c r="F273" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G273" t="str">
+        <v>w</v>
+      </c>
+      <c r="H273">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>9</v>
+      </c>
+      <c r="B274" s="1">
+        <v>45444.083333333336</v>
+      </c>
+      <c r="C274" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D274" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E274" t="str">
+        <v>25,7</v>
+      </c>
+      <c r="F274" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G274" t="str">
+        <v>w</v>
+      </c>
+      <c r="H274">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>9</v>
+      </c>
+      <c r="B275" s="1">
+        <v>45689.041666666664</v>
+      </c>
+      <c r="C275" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D275" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E275" t="str">
+        <v>22,6</v>
+      </c>
+      <c r="F275" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G275" t="str">
+        <v>w</v>
+      </c>
+      <c r="H275">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>12</v>
+      </c>
+      <c r="B276" s="1">
+        <v>44197.041666666664</v>
+      </c>
+      <c r="C276" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D276" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E276" t="str">
+        <v>59,1</v>
+      </c>
+      <c r="F276" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G276" t="str">
+        <v>w</v>
+      </c>
+      <c r="H276">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>12</v>
+      </c>
+      <c r="B277" s="1">
+        <v>44199.041666666664</v>
+      </c>
+      <c r="C277" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D277" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E277" t="str">
+        <v>39,5</v>
+      </c>
+      <c r="F277" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G277" t="str">
+        <v>w</v>
+      </c>
+      <c r="H277">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>12</v>
+      </c>
+      <c r="B278" s="1">
+        <v>44216.041666666664</v>
+      </c>
+      <c r="C278" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D278" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E278" t="str">
+        <v>55,8</v>
+      </c>
+      <c r="F278" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G278" t="str">
+        <v>w</v>
+      </c>
+      <c r="H278">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>12</v>
+      </c>
+      <c r="B279" s="1">
+        <v>44242.041666666664</v>
+      </c>
+      <c r="C279" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D279" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E279" t="str">
+        <v>59,1</v>
+      </c>
+      <c r="F279" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G279" t="str">
+        <v>w</v>
+      </c>
+      <c r="H279">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>12</v>
+      </c>
+      <c r="B280" s="1">
+        <v>44244.041666666664</v>
+      </c>
+      <c r="C280" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D280" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E280" t="str">
+        <v>41,2</v>
+      </c>
+      <c r="F280" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G280" t="str">
+        <v>w</v>
+      </c>
+      <c r="H280">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>12</v>
+      </c>
+      <c r="B281" s="1">
+        <v>44265.041666666664</v>
+      </c>
+      <c r="C281" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D281" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E281" t="str">
+        <v>55,8</v>
+      </c>
+      <c r="F281" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G281" t="str">
+        <v>w</v>
+      </c>
+      <c r="H281">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>12</v>
+      </c>
+      <c r="B282" s="1">
+        <v>44287.083333333336</v>
+      </c>
+      <c r="C282" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D282" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E282" t="str">
+        <v>59,1</v>
+      </c>
+      <c r="F282" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G282" t="str">
+        <v>w</v>
+      </c>
+      <c r="H282">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>12</v>
+      </c>
+      <c r="B283" s="1">
+        <v>44289.083333333336</v>
+      </c>
+      <c r="C283" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D283" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E283" t="str">
+        <v>25,0</v>
+      </c>
+      <c r="F283" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G283" t="str">
+        <v>w</v>
+      </c>
+      <c r="H283">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>12</v>
+      </c>
+      <c r="B284" s="1">
+        <v>44306.083333333336</v>
+      </c>
+      <c r="C284" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D284" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E284" t="str">
+        <v>47,5</v>
+      </c>
+      <c r="F284" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G284" t="str">
+        <v>w</v>
+      </c>
+      <c r="H284">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>12</v>
+      </c>
+      <c r="B285" s="1">
+        <v>44348.083333333336</v>
+      </c>
+      <c r="C285" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D285" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E285" t="str">
+        <v>53,9</v>
+      </c>
+      <c r="F285" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G285" t="str">
+        <v>w</v>
+      </c>
+      <c r="H285">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H217"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H285"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/test_labs.xlsx
+++ b/public/test_labs.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H285"/>
+  <dimension ref="A1:H283"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5961,7 +5961,7 @@
     </row>
     <row r="218">
       <c r="A218">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B218" s="1">
         <v>44562.041666666664</v>
@@ -5973,24 +5973,24 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E218" t="str">
-        <v>74,1</v>
+        <v>91,7</v>
       </c>
       <c r="F218" t="str">
         <v>98979-8</v>
       </c>
       <c r="G218" t="str">
-        <v>w</v>
+        <v>m</v>
       </c>
       <c r="H218">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="219">
       <c r="A219">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B219" s="1">
-        <v>45292.041666666664</v>
+        <v>44652.083333333336</v>
       </c>
       <c r="C219" t="str">
         <v>eGFR</v>
@@ -5999,16 +5999,16 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E219" t="str">
-        <v>43,1</v>
+        <v>86,5</v>
       </c>
       <c r="F219" t="str">
         <v>98979-8</v>
       </c>
       <c r="G219" t="str">
-        <v>w</v>
+        <v>m</v>
       </c>
       <c r="H219">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="220">
@@ -6016,7 +6016,7 @@
         <v>4</v>
       </c>
       <c r="B220" s="1">
-        <v>44562.041666666664</v>
+        <v>44742.083333333336</v>
       </c>
       <c r="C220" t="str">
         <v>eGFR</v>
@@ -6025,7 +6025,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E220" t="str">
-        <v>91,7</v>
+        <v>81,8</v>
       </c>
       <c r="F220" t="str">
         <v>98979-8</v>
@@ -6042,7 +6042,7 @@
         <v>4</v>
       </c>
       <c r="B221" s="1">
-        <v>44652.083333333336</v>
+        <v>44832.083333333336</v>
       </c>
       <c r="C221" t="str">
         <v>eGFR</v>
@@ -6051,7 +6051,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E221" t="str">
-        <v>86,5</v>
+        <v>79,5</v>
       </c>
       <c r="F221" t="str">
         <v>98979-8</v>
@@ -6060,7 +6060,7 @@
         <v>m</v>
       </c>
       <c r="H221">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="222">
@@ -6068,7 +6068,7 @@
         <v>4</v>
       </c>
       <c r="B222" s="1">
-        <v>44742.083333333336</v>
+        <v>44922.041666666664</v>
       </c>
       <c r="C222" t="str">
         <v>eGFR</v>
@@ -6077,7 +6077,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E222" t="str">
-        <v>81,8</v>
+        <v>73,2</v>
       </c>
       <c r="F222" t="str">
         <v>98979-8</v>
@@ -6086,7 +6086,7 @@
         <v>m</v>
       </c>
       <c r="H222">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="223">
@@ -6094,7 +6094,7 @@
         <v>4</v>
       </c>
       <c r="B223" s="1">
-        <v>44832.083333333336</v>
+        <v>45012.083333333336</v>
       </c>
       <c r="C223" t="str">
         <v>eGFR</v>
@@ -6103,7 +6103,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E223" t="str">
-        <v>79,5</v>
+        <v>69,7</v>
       </c>
       <c r="F223" t="str">
         <v>98979-8</v>
@@ -6120,7 +6120,7 @@
         <v>4</v>
       </c>
       <c r="B224" s="1">
-        <v>44922.041666666664</v>
+        <v>45102.083333333336</v>
       </c>
       <c r="C224" t="str">
         <v>eGFR</v>
@@ -6129,7 +6129,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E224" t="str">
-        <v>73,2</v>
+        <v>66,5</v>
       </c>
       <c r="F224" t="str">
         <v>98979-8</v>
@@ -6146,7 +6146,7 @@
         <v>4</v>
       </c>
       <c r="B225" s="1">
-        <v>45012.083333333336</v>
+        <v>45192.083333333336</v>
       </c>
       <c r="C225" t="str">
         <v>eGFR</v>
@@ -6155,7 +6155,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E225" t="str">
-        <v>69,7</v>
+        <v>63,2</v>
       </c>
       <c r="F225" t="str">
         <v>98979-8</v>
@@ -6164,15 +6164,15 @@
         <v>m</v>
       </c>
       <c r="H225">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="226">
       <c r="A226">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B226" s="1">
-        <v>45102.083333333336</v>
+        <v>44571.041666666664</v>
       </c>
       <c r="C226" t="str">
         <v>eGFR</v>
@@ -6181,7 +6181,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E226" t="str">
-        <v>66,5</v>
+        <v>65,5</v>
       </c>
       <c r="F226" t="str">
         <v>98979-8</v>
@@ -6190,15 +6190,15 @@
         <v>m</v>
       </c>
       <c r="H226">
-        <v>51</v>
+        <v>69</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B227" s="1">
-        <v>45192.083333333336</v>
+        <v>44661.083333333336</v>
       </c>
       <c r="C227" t="str">
         <v>eGFR</v>
@@ -6207,7 +6207,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E227" t="str">
-        <v>63,2</v>
+        <v>62,3</v>
       </c>
       <c r="F227" t="str">
         <v>98979-8</v>
@@ -6216,7 +6216,7 @@
         <v>m</v>
       </c>
       <c r="H227">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
     <row r="228">
@@ -6224,7 +6224,7 @@
         <v>6</v>
       </c>
       <c r="B228" s="1">
-        <v>44571.041666666664</v>
+        <v>44752.083333333336</v>
       </c>
       <c r="C228" t="str">
         <v>eGFR</v>
@@ -6233,7 +6233,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E228" t="str">
-        <v>65,5</v>
+        <v>59,5</v>
       </c>
       <c r="F228" t="str">
         <v>98979-8</v>
@@ -6250,7 +6250,7 @@
         <v>6</v>
       </c>
       <c r="B229" s="1">
-        <v>44661.083333333336</v>
+        <v>44809.083333333336</v>
       </c>
       <c r="C229" t="str">
         <v>eGFR</v>
@@ -6259,7 +6259,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E229" t="str">
-        <v>62,3</v>
+        <v>59,1</v>
       </c>
       <c r="F229" t="str">
         <v>98979-8</v>
@@ -6268,7 +6268,7 @@
         <v>m</v>
       </c>
       <c r="H229">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="230">
@@ -6276,7 +6276,7 @@
         <v>6</v>
       </c>
       <c r="B230" s="1">
-        <v>44752.083333333336</v>
+        <v>44812.083333333336</v>
       </c>
       <c r="C230" t="str">
         <v>eGFR</v>
@@ -6285,7 +6285,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E230" t="str">
-        <v>59,5</v>
+        <v>22,6</v>
       </c>
       <c r="F230" t="str">
         <v>98979-8</v>
@@ -6294,7 +6294,7 @@
         <v>m</v>
       </c>
       <c r="H230">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="231">
@@ -6302,7 +6302,7 @@
         <v>6</v>
       </c>
       <c r="B231" s="1">
-        <v>44809.083333333336</v>
+        <v>44820.083333333336</v>
       </c>
       <c r="C231" t="str">
         <v>eGFR</v>
@@ -6311,7 +6311,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E231" t="str">
-        <v>59,1</v>
+        <v>35,2</v>
       </c>
       <c r="F231" t="str">
         <v>98979-8</v>
@@ -6328,7 +6328,7 @@
         <v>6</v>
       </c>
       <c r="B232" s="1">
-        <v>44812.083333333336</v>
+        <v>44832.083333333336</v>
       </c>
       <c r="C232" t="str">
         <v>eGFR</v>
@@ -6337,7 +6337,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E232" t="str">
-        <v>22,6</v>
+        <v>49,8</v>
       </c>
       <c r="F232" t="str">
         <v>98979-8</v>
@@ -6354,7 +6354,7 @@
         <v>6</v>
       </c>
       <c r="B233" s="1">
-        <v>44820.083333333336</v>
+        <v>44905.041666666664</v>
       </c>
       <c r="C233" t="str">
         <v>eGFR</v>
@@ -6363,7 +6363,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E233" t="str">
-        <v>35,2</v>
+        <v>56,5</v>
       </c>
       <c r="F233" t="str">
         <v>98979-8</v>
@@ -6380,7 +6380,7 @@
         <v>6</v>
       </c>
       <c r="B234" s="1">
-        <v>44832.083333333336</v>
+        <v>44995.041666666664</v>
       </c>
       <c r="C234" t="str">
         <v>eGFR</v>
@@ -6389,7 +6389,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E234" t="str">
-        <v>49,8</v>
+        <v>54,1</v>
       </c>
       <c r="F234" t="str">
         <v>98979-8</v>
@@ -6406,7 +6406,7 @@
         <v>6</v>
       </c>
       <c r="B235" s="1">
-        <v>44905.041666666664</v>
+        <v>45087.083333333336</v>
       </c>
       <c r="C235" t="str">
         <v>eGFR</v>
@@ -6415,7 +6415,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E235" t="str">
-        <v>56,5</v>
+        <v>51,8</v>
       </c>
       <c r="F235" t="str">
         <v>98979-8</v>
@@ -6432,7 +6432,7 @@
         <v>6</v>
       </c>
       <c r="B236" s="1">
-        <v>44995.041666666664</v>
+        <v>45179.083333333336</v>
       </c>
       <c r="C236" t="str">
         <v>eGFR</v>
@@ -6441,7 +6441,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E236" t="str">
-        <v>54,1</v>
+        <v>49,5</v>
       </c>
       <c r="F236" t="str">
         <v>98979-8</v>
@@ -6450,15 +6450,15 @@
         <v>m</v>
       </c>
       <c r="H236">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B237" s="1">
-        <v>45087.083333333336</v>
+        <v>44197.041666666664</v>
       </c>
       <c r="C237" t="str">
         <v>eGFR</v>
@@ -6467,7 +6467,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E237" t="str">
-        <v>51,8</v>
+        <v>80,0</v>
       </c>
       <c r="F237" t="str">
         <v>98979-8</v>
@@ -6476,15 +6476,15 @@
         <v>m</v>
       </c>
       <c r="H237">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="238">
       <c r="A238">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B238" s="1">
-        <v>45179.083333333336</v>
+        <v>44256.041666666664</v>
       </c>
       <c r="C238" t="str">
         <v>eGFR</v>
@@ -6493,7 +6493,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E238" t="str">
-        <v>49,5</v>
+        <v>75,4</v>
       </c>
       <c r="F238" t="str">
         <v>98979-8</v>
@@ -6502,7 +6502,7 @@
         <v>m</v>
       </c>
       <c r="H238">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="239">
@@ -6510,7 +6510,7 @@
         <v>7</v>
       </c>
       <c r="B239" s="1">
-        <v>44197.041666666664</v>
+        <v>44348.083333333336</v>
       </c>
       <c r="C239" t="str">
         <v>eGFR</v>
@@ -6519,7 +6519,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E239" t="str">
-        <v>80,0</v>
+        <v>71,3</v>
       </c>
       <c r="F239" t="str">
         <v>98979-8</v>
@@ -6536,7 +6536,7 @@
         <v>7</v>
       </c>
       <c r="B240" s="1">
-        <v>44256.041666666664</v>
+        <v>44350.083333333336</v>
       </c>
       <c r="C240" t="str">
         <v>eGFR</v>
@@ -6545,7 +6545,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E240" t="str">
-        <v>75,4</v>
+        <v>47,3</v>
       </c>
       <c r="F240" t="str">
         <v>98979-8</v>
@@ -6562,7 +6562,7 @@
         <v>7</v>
       </c>
       <c r="B241" s="1">
-        <v>44348.083333333336</v>
+        <v>44359.083333333336</v>
       </c>
       <c r="C241" t="str">
         <v>eGFR</v>
@@ -6571,7 +6571,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E241" t="str">
-        <v>71,3</v>
+        <v>64,3</v>
       </c>
       <c r="F241" t="str">
         <v>98979-8</v>
@@ -6588,7 +6588,7 @@
         <v>7</v>
       </c>
       <c r="B242" s="1">
-        <v>44350.083333333336</v>
+        <v>44440.083333333336</v>
       </c>
       <c r="C242" t="str">
         <v>eGFR</v>
@@ -6597,7 +6597,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E242" t="str">
-        <v>47,3</v>
+        <v>70,9</v>
       </c>
       <c r="F242" t="str">
         <v>98979-8</v>
@@ -6606,7 +6606,7 @@
         <v>m</v>
       </c>
       <c r="H242">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="243">
@@ -6614,7 +6614,7 @@
         <v>7</v>
       </c>
       <c r="B243" s="1">
-        <v>44359.083333333336</v>
+        <v>44562.041666666664</v>
       </c>
       <c r="C243" t="str">
         <v>eGFR</v>
@@ -6623,7 +6623,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E243" t="str">
-        <v>64,3</v>
+        <v>67,2</v>
       </c>
       <c r="F243" t="str">
         <v>98979-8</v>
@@ -6632,7 +6632,7 @@
         <v>m</v>
       </c>
       <c r="H243">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="244">
@@ -6640,7 +6640,7 @@
         <v>7</v>
       </c>
       <c r="B244" s="1">
-        <v>44440.083333333336</v>
+        <v>44565.041666666664</v>
       </c>
       <c r="C244" t="str">
         <v>eGFR</v>
@@ -6649,7 +6649,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E244" t="str">
-        <v>70,9</v>
+        <v>28,5</v>
       </c>
       <c r="F244" t="str">
         <v>98979-8</v>
@@ -6666,7 +6666,7 @@
         <v>7</v>
       </c>
       <c r="B245" s="1">
-        <v>44562.041666666664</v>
+        <v>44581.041666666664</v>
       </c>
       <c r="C245" t="str">
         <v>eGFR</v>
@@ -6675,7 +6675,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E245" t="str">
-        <v>67,2</v>
+        <v>55,4</v>
       </c>
       <c r="F245" t="str">
         <v>98979-8</v>
@@ -6692,7 +6692,7 @@
         <v>7</v>
       </c>
       <c r="B246" s="1">
-        <v>44565.041666666664</v>
+        <v>44713.083333333336</v>
       </c>
       <c r="C246" t="str">
         <v>eGFR</v>
@@ -6701,7 +6701,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E246" t="str">
-        <v>28,5</v>
+        <v>63,9</v>
       </c>
       <c r="F246" t="str">
         <v>98979-8</v>
@@ -6718,7 +6718,7 @@
         <v>7</v>
       </c>
       <c r="B247" s="1">
-        <v>44581.041666666664</v>
+        <v>44835.083333333336</v>
       </c>
       <c r="C247" t="str">
         <v>eGFR</v>
@@ -6727,7 +6727,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E247" t="str">
-        <v>55,4</v>
+        <v>60,4</v>
       </c>
       <c r="F247" t="str">
         <v>98979-8</v>
@@ -6736,7 +6736,7 @@
         <v>m</v>
       </c>
       <c r="H247">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="248">
@@ -6744,7 +6744,7 @@
         <v>7</v>
       </c>
       <c r="B248" s="1">
-        <v>44713.083333333336</v>
+        <v>44837.083333333336</v>
       </c>
       <c r="C248" t="str">
         <v>eGFR</v>
@@ -6753,7 +6753,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E248" t="str">
-        <v>63,9</v>
+        <v>14,1</v>
       </c>
       <c r="F248" t="str">
         <v>98979-8</v>
@@ -6762,7 +6762,7 @@
         <v>m</v>
       </c>
       <c r="H248">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="249">
@@ -6770,7 +6770,7 @@
         <v>7</v>
       </c>
       <c r="B249" s="1">
-        <v>44835.083333333336</v>
+        <v>44852.083333333336</v>
       </c>
       <c r="C249" t="str">
         <v>eGFR</v>
@@ -6779,7 +6779,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E249" t="str">
-        <v>60,4</v>
+        <v>34,4</v>
       </c>
       <c r="F249" t="str">
         <v>98979-8</v>
@@ -6796,7 +6796,7 @@
         <v>7</v>
       </c>
       <c r="B250" s="1">
-        <v>44837.083333333336</v>
+        <v>44927.041666666664</v>
       </c>
       <c r="C250" t="str">
         <v>eGFR</v>
@@ -6805,7 +6805,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E250" t="str">
-        <v>14,1</v>
+        <v>55,1</v>
       </c>
       <c r="F250" t="str">
         <v>98979-8</v>
@@ -6822,7 +6822,7 @@
         <v>7</v>
       </c>
       <c r="B251" s="1">
-        <v>44852.083333333336</v>
+        <v>45078.083333333336</v>
       </c>
       <c r="C251" t="str">
         <v>eGFR</v>
@@ -6831,7 +6831,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E251" t="str">
-        <v>34,4</v>
+        <v>52,7</v>
       </c>
       <c r="F251" t="str">
         <v>98979-8</v>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="252">
       <c r="A252">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B252" s="1">
-        <v>44927.041666666664</v>
+        <v>43862.041666666664</v>
       </c>
       <c r="C252" t="str">
         <v>eGFR</v>
@@ -6857,24 +6857,24 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E252" t="str">
-        <v>55,1</v>
+        <v>69,9</v>
       </c>
       <c r="F252" t="str">
         <v>98979-8</v>
       </c>
       <c r="G252" t="str">
-        <v>m</v>
+        <v>w</v>
       </c>
       <c r="H252">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="253">
       <c r="A253">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B253" s="1">
-        <v>45078.083333333336</v>
+        <v>44044.083333333336</v>
       </c>
       <c r="C253" t="str">
         <v>eGFR</v>
@@ -6883,16 +6883,16 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E253" t="str">
-        <v>52,7</v>
+        <v>68,2</v>
       </c>
       <c r="F253" t="str">
         <v>98979-8</v>
       </c>
       <c r="G253" t="str">
-        <v>m</v>
+        <v>w</v>
       </c>
       <c r="H253">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="254">
@@ -6900,7 +6900,7 @@
         <v>8</v>
       </c>
       <c r="B254" s="1">
-        <v>43862.041666666664</v>
+        <v>44228.041666666664</v>
       </c>
       <c r="C254" t="str">
         <v>eGFR</v>
@@ -6909,7 +6909,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E254" t="str">
-        <v>69,9</v>
+        <v>68,6</v>
       </c>
       <c r="F254" t="str">
         <v>98979-8</v>
@@ -6918,7 +6918,7 @@
         <v>w</v>
       </c>
       <c r="H254">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="255">
@@ -6926,7 +6926,7 @@
         <v>8</v>
       </c>
       <c r="B255" s="1">
-        <v>44044.083333333336</v>
+        <v>44409.083333333336</v>
       </c>
       <c r="C255" t="str">
         <v>eGFR</v>
@@ -6935,7 +6935,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E255" t="str">
-        <v>68,2</v>
+        <v>66,9</v>
       </c>
       <c r="F255" t="str">
         <v>98979-8</v>
@@ -6944,7 +6944,7 @@
         <v>w</v>
       </c>
       <c r="H255">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="256">
@@ -6952,7 +6952,7 @@
         <v>8</v>
       </c>
       <c r="B256" s="1">
-        <v>44228.041666666664</v>
+        <v>44593.041666666664</v>
       </c>
       <c r="C256" t="str">
         <v>eGFR</v>
@@ -6961,7 +6961,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E256" t="str">
-        <v>68,6</v>
+        <v>65,7</v>
       </c>
       <c r="F256" t="str">
         <v>98979-8</v>
@@ -6970,7 +6970,7 @@
         <v>w</v>
       </c>
       <c r="H256">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="257">
@@ -6978,7 +6978,7 @@
         <v>8</v>
       </c>
       <c r="B257" s="1">
-        <v>44409.083333333336</v>
+        <v>44774.083333333336</v>
       </c>
       <c r="C257" t="str">
         <v>eGFR</v>
@@ -6987,7 +6987,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E257" t="str">
-        <v>66,9</v>
+        <v>67,3</v>
       </c>
       <c r="F257" t="str">
         <v>98979-8</v>
@@ -6996,7 +6996,7 @@
         <v>w</v>
       </c>
       <c r="H257">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="258">
@@ -7004,7 +7004,7 @@
         <v>8</v>
       </c>
       <c r="B258" s="1">
-        <v>44593.041666666664</v>
+        <v>44958.041666666664</v>
       </c>
       <c r="C258" t="str">
         <v>eGFR</v>
@@ -7013,7 +7013,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E258" t="str">
-        <v>65,7</v>
+        <v>66,1</v>
       </c>
       <c r="F258" t="str">
         <v>98979-8</v>
@@ -7022,7 +7022,7 @@
         <v>w</v>
       </c>
       <c r="H258">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="259">
@@ -7030,7 +7030,7 @@
         <v>8</v>
       </c>
       <c r="B259" s="1">
-        <v>44774.083333333336</v>
+        <v>45139.083333333336</v>
       </c>
       <c r="C259" t="str">
         <v>eGFR</v>
@@ -7039,7 +7039,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E259" t="str">
-        <v>67,3</v>
+        <v>64,5</v>
       </c>
       <c r="F259" t="str">
         <v>98979-8</v>
@@ -7048,7 +7048,7 @@
         <v>w</v>
       </c>
       <c r="H259">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="260">
@@ -7056,7 +7056,7 @@
         <v>8</v>
       </c>
       <c r="B260" s="1">
-        <v>44958.041666666664</v>
+        <v>45323.041666666664</v>
       </c>
       <c r="C260" t="str">
         <v>eGFR</v>
@@ -7065,7 +7065,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E260" t="str">
-        <v>66,1</v>
+        <v>64,9</v>
       </c>
       <c r="F260" t="str">
         <v>98979-8</v>
@@ -7074,7 +7074,7 @@
         <v>w</v>
       </c>
       <c r="H260">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="261">
@@ -7082,7 +7082,7 @@
         <v>8</v>
       </c>
       <c r="B261" s="1">
-        <v>45139.083333333336</v>
+        <v>45505.083333333336</v>
       </c>
       <c r="C261" t="str">
         <v>eGFR</v>
@@ -7091,7 +7091,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E261" t="str">
-        <v>64,5</v>
+        <v>63,4</v>
       </c>
       <c r="F261" t="str">
         <v>98979-8</v>
@@ -7100,7 +7100,7 @@
         <v>w</v>
       </c>
       <c r="H261">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="262">
@@ -7108,7 +7108,7 @@
         <v>8</v>
       </c>
       <c r="B262" s="1">
-        <v>45323.041666666664</v>
+        <v>45689.041666666664</v>
       </c>
       <c r="C262" t="str">
         <v>eGFR</v>
@@ -7117,7 +7117,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E262" t="str">
-        <v>64,9</v>
+        <v>63,7</v>
       </c>
       <c r="F262" t="str">
         <v>98979-8</v>
@@ -7126,7 +7126,7 @@
         <v>w</v>
       </c>
       <c r="H262">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="263">
@@ -7134,7 +7134,7 @@
         <v>8</v>
       </c>
       <c r="B263" s="1">
-        <v>45505.083333333336</v>
+        <v>45870.083333333336</v>
       </c>
       <c r="C263" t="str">
         <v>eGFR</v>
@@ -7143,7 +7143,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E263" t="str">
-        <v>63,4</v>
+        <v>62,2</v>
       </c>
       <c r="F263" t="str">
         <v>98979-8</v>
@@ -7152,15 +7152,15 @@
         <v>w</v>
       </c>
       <c r="H263">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="264">
       <c r="A264">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B264" s="1">
-        <v>45689.041666666664</v>
+        <v>43497.041666666664</v>
       </c>
       <c r="C264" t="str">
         <v>eGFR</v>
@@ -7169,7 +7169,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E264" t="str">
-        <v>63,7</v>
+        <v>68,2</v>
       </c>
       <c r="F264" t="str">
         <v>98979-8</v>
@@ -7178,15 +7178,15 @@
         <v>w</v>
       </c>
       <c r="H264">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="265">
       <c r="A265">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B265" s="1">
-        <v>45870.083333333336</v>
+        <v>43739.083333333336</v>
       </c>
       <c r="C265" t="str">
         <v>eGFR</v>
@@ -7195,7 +7195,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E265" t="str">
-        <v>62,2</v>
+        <v>61,4</v>
       </c>
       <c r="F265" t="str">
         <v>98979-8</v>
@@ -7204,7 +7204,7 @@
         <v>w</v>
       </c>
       <c r="H265">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="266">
@@ -7212,7 +7212,7 @@
         <v>9</v>
       </c>
       <c r="B266" s="1">
-        <v>43497.041666666664</v>
+        <v>43983.083333333336</v>
       </c>
       <c r="C266" t="str">
         <v>eGFR</v>
@@ -7221,7 +7221,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E266" t="str">
-        <v>68,2</v>
+        <v>56,0</v>
       </c>
       <c r="F266" t="str">
         <v>98979-8</v>
@@ -7230,7 +7230,7 @@
         <v>w</v>
       </c>
       <c r="H266">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="267">
@@ -7238,7 +7238,7 @@
         <v>9</v>
       </c>
       <c r="B267" s="1">
-        <v>43739.083333333336</v>
+        <v>44228.041666666664</v>
       </c>
       <c r="C267" t="str">
         <v>eGFR</v>
@@ -7247,7 +7247,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E267" t="str">
-        <v>61,4</v>
+        <v>50,0</v>
       </c>
       <c r="F267" t="str">
         <v>98979-8</v>
@@ -7256,7 +7256,7 @@
         <v>w</v>
       </c>
       <c r="H267">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="268">
@@ -7264,7 +7264,7 @@
         <v>9</v>
       </c>
       <c r="B268" s="1">
-        <v>43983.083333333336</v>
+        <v>44470.083333333336</v>
       </c>
       <c r="C268" t="str">
         <v>eGFR</v>
@@ -7273,7 +7273,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E268" t="str">
-        <v>56,0</v>
+        <v>43,4</v>
       </c>
       <c r="F268" t="str">
         <v>98979-8</v>
@@ -7282,7 +7282,7 @@
         <v>w</v>
       </c>
       <c r="H268">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="269">
@@ -7290,7 +7290,7 @@
         <v>9</v>
       </c>
       <c r="B269" s="1">
-        <v>44228.041666666664</v>
+        <v>44713.083333333336</v>
       </c>
       <c r="C269" t="str">
         <v>eGFR</v>
@@ -7299,7 +7299,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E269" t="str">
-        <v>50,0</v>
+        <v>37,9</v>
       </c>
       <c r="F269" t="str">
         <v>98979-8</v>
@@ -7308,7 +7308,7 @@
         <v>w</v>
       </c>
       <c r="H269">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="270">
@@ -7316,7 +7316,7 @@
         <v>9</v>
       </c>
       <c r="B270" s="1">
-        <v>44470.083333333336</v>
+        <v>44958.041666666664</v>
       </c>
       <c r="C270" t="str">
         <v>eGFR</v>
@@ -7325,7 +7325,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E270" t="str">
-        <v>43,4</v>
+        <v>33,0</v>
       </c>
       <c r="F270" t="str">
         <v>98979-8</v>
@@ -7334,7 +7334,7 @@
         <v>w</v>
       </c>
       <c r="H270">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="271">
@@ -7342,7 +7342,7 @@
         <v>9</v>
       </c>
       <c r="B271" s="1">
-        <v>44713.083333333336</v>
+        <v>45200.083333333336</v>
       </c>
       <c r="C271" t="str">
         <v>eGFR</v>
@@ -7351,7 +7351,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E271" t="str">
-        <v>37,9</v>
+        <v>29,2</v>
       </c>
       <c r="F271" t="str">
         <v>98979-8</v>
@@ -7360,7 +7360,7 @@
         <v>w</v>
       </c>
       <c r="H271">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="272">
@@ -7368,7 +7368,7 @@
         <v>9</v>
       </c>
       <c r="B272" s="1">
-        <v>44958.041666666664</v>
+        <v>45444.083333333336</v>
       </c>
       <c r="C272" t="str">
         <v>eGFR</v>
@@ -7377,7 +7377,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E272" t="str">
-        <v>33,0</v>
+        <v>25,7</v>
       </c>
       <c r="F272" t="str">
         <v>98979-8</v>
@@ -7386,7 +7386,7 @@
         <v>w</v>
       </c>
       <c r="H272">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="273">
@@ -7394,7 +7394,7 @@
         <v>9</v>
       </c>
       <c r="B273" s="1">
-        <v>45200.083333333336</v>
+        <v>45689.041666666664</v>
       </c>
       <c r="C273" t="str">
         <v>eGFR</v>
@@ -7403,7 +7403,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E273" t="str">
-        <v>29,2</v>
+        <v>22,6</v>
       </c>
       <c r="F273" t="str">
         <v>98979-8</v>
@@ -7412,15 +7412,15 @@
         <v>w</v>
       </c>
       <c r="H273">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="274">
       <c r="A274">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B274" s="1">
-        <v>45444.083333333336</v>
+        <v>44197.041666666664</v>
       </c>
       <c r="C274" t="str">
         <v>eGFR</v>
@@ -7429,7 +7429,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E274" t="str">
-        <v>25,7</v>
+        <v>59,1</v>
       </c>
       <c r="F274" t="str">
         <v>98979-8</v>
@@ -7438,15 +7438,15 @@
         <v>w</v>
       </c>
       <c r="H274">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="275">
       <c r="A275">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B275" s="1">
-        <v>45689.041666666664</v>
+        <v>44199.041666666664</v>
       </c>
       <c r="C275" t="str">
         <v>eGFR</v>
@@ -7455,7 +7455,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E275" t="str">
-        <v>22,6</v>
+        <v>39,5</v>
       </c>
       <c r="F275" t="str">
         <v>98979-8</v>
@@ -7464,7 +7464,7 @@
         <v>w</v>
       </c>
       <c r="H275">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="276">
@@ -7472,7 +7472,7 @@
         <v>12</v>
       </c>
       <c r="B276" s="1">
-        <v>44197.041666666664</v>
+        <v>44216.041666666664</v>
       </c>
       <c r="C276" t="str">
         <v>eGFR</v>
@@ -7481,7 +7481,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E276" t="str">
-        <v>59,1</v>
+        <v>55,8</v>
       </c>
       <c r="F276" t="str">
         <v>98979-8</v>
@@ -7498,7 +7498,7 @@
         <v>12</v>
       </c>
       <c r="B277" s="1">
-        <v>44199.041666666664</v>
+        <v>44242.041666666664</v>
       </c>
       <c r="C277" t="str">
         <v>eGFR</v>
@@ -7507,7 +7507,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E277" t="str">
-        <v>39,5</v>
+        <v>59,1</v>
       </c>
       <c r="F277" t="str">
         <v>98979-8</v>
@@ -7524,7 +7524,7 @@
         <v>12</v>
       </c>
       <c r="B278" s="1">
-        <v>44216.041666666664</v>
+        <v>44244.041666666664</v>
       </c>
       <c r="C278" t="str">
         <v>eGFR</v>
@@ -7533,7 +7533,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E278" t="str">
-        <v>55,8</v>
+        <v>41,2</v>
       </c>
       <c r="F278" t="str">
         <v>98979-8</v>
@@ -7550,7 +7550,7 @@
         <v>12</v>
       </c>
       <c r="B279" s="1">
-        <v>44242.041666666664</v>
+        <v>44265.041666666664</v>
       </c>
       <c r="C279" t="str">
         <v>eGFR</v>
@@ -7559,7 +7559,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E279" t="str">
-        <v>59,1</v>
+        <v>55,8</v>
       </c>
       <c r="F279" t="str">
         <v>98979-8</v>
@@ -7576,7 +7576,7 @@
         <v>12</v>
       </c>
       <c r="B280" s="1">
-        <v>44244.041666666664</v>
+        <v>44287.083333333336</v>
       </c>
       <c r="C280" t="str">
         <v>eGFR</v>
@@ -7585,7 +7585,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E280" t="str">
-        <v>41,2</v>
+        <v>59,1</v>
       </c>
       <c r="F280" t="str">
         <v>98979-8</v>
@@ -7602,7 +7602,7 @@
         <v>12</v>
       </c>
       <c r="B281" s="1">
-        <v>44265.041666666664</v>
+        <v>44289.083333333336</v>
       </c>
       <c r="C281" t="str">
         <v>eGFR</v>
@@ -7611,7 +7611,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E281" t="str">
-        <v>55,8</v>
+        <v>25,0</v>
       </c>
       <c r="F281" t="str">
         <v>98979-8</v>
@@ -7628,7 +7628,7 @@
         <v>12</v>
       </c>
       <c r="B282" s="1">
-        <v>44287.083333333336</v>
+        <v>44306.083333333336</v>
       </c>
       <c r="C282" t="str">
         <v>eGFR</v>
@@ -7637,7 +7637,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E282" t="str">
-        <v>59,1</v>
+        <v>47,5</v>
       </c>
       <c r="F282" t="str">
         <v>98979-8</v>
@@ -7654,7 +7654,7 @@
         <v>12</v>
       </c>
       <c r="B283" s="1">
-        <v>44289.083333333336</v>
+        <v>44348.083333333336</v>
       </c>
       <c r="C283" t="str">
         <v>eGFR</v>
@@ -7663,7 +7663,7 @@
         <v>ml/min/1,73m²</v>
       </c>
       <c r="E283" t="str">
-        <v>25,0</v>
+        <v>53,9</v>
       </c>
       <c r="F283" t="str">
         <v>98979-8</v>
@@ -7675,61 +7675,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="284">
-      <c r="A284">
-        <v>12</v>
-      </c>
-      <c r="B284" s="1">
-        <v>44306.083333333336</v>
-      </c>
-      <c r="C284" t="str">
-        <v>eGFR</v>
-      </c>
-      <c r="D284" t="str">
-        <v>ml/min/1,73m²</v>
-      </c>
-      <c r="E284" t="str">
-        <v>47,5</v>
-      </c>
-      <c r="F284" t="str">
-        <v>98979-8</v>
-      </c>
-      <c r="G284" t="str">
-        <v>w</v>
-      </c>
-      <c r="H284">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285">
-        <v>12</v>
-      </c>
-      <c r="B285" s="1">
-        <v>44348.083333333336</v>
-      </c>
-      <c r="C285" t="str">
-        <v>eGFR</v>
-      </c>
-      <c r="D285" t="str">
-        <v>ml/min/1,73m²</v>
-      </c>
-      <c r="E285" t="str">
-        <v>53,9</v>
-      </c>
-      <c r="F285" t="str">
-        <v>98979-8</v>
-      </c>
-      <c r="G285" t="str">
-        <v>w</v>
-      </c>
-      <c r="H285">
-        <v>74</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H285"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H283"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/test_labs.xlsx
+++ b/public/test_labs.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H283"/>
+  <dimension ref="A1:H475"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7675,9 +7675,5001 @@
         <v>74</v>
       </c>
     </row>
+    <row r="284">
+      <c r="A284">
+        <v>15</v>
+      </c>
+      <c r="B284" s="1">
+        <v>44214.041666666664</v>
+      </c>
+      <c r="C284" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D284" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E284" t="str">
+        <v>0,86</v>
+      </c>
+      <c r="F284" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G284" t="str">
+        <v>w</v>
+      </c>
+      <c r="H284">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>15</v>
+      </c>
+      <c r="B285" s="1">
+        <v>44214.041666666664</v>
+      </c>
+      <c r="C285" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D285" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E285" t="str">
+        <v>87,0</v>
+      </c>
+      <c r="F285" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G285" t="str">
+        <v>w</v>
+      </c>
+      <c r="H285">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>15</v>
+      </c>
+      <c r="B286" s="1">
+        <v>44398.083333333336</v>
+      </c>
+      <c r="C286" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D286" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E286" t="str">
+        <v>0,88</v>
+      </c>
+      <c r="F286" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G286" t="str">
+        <v>w</v>
+      </c>
+      <c r="H286">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>15</v>
+      </c>
+      <c r="B287" s="1">
+        <v>44398.083333333336</v>
+      </c>
+      <c r="C287" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D287" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E287" t="str">
+        <v>84,6</v>
+      </c>
+      <c r="F287" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G287" t="str">
+        <v>w</v>
+      </c>
+      <c r="H287">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>15</v>
+      </c>
+      <c r="B288" s="1">
+        <v>44575.041666666664</v>
+      </c>
+      <c r="C288" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D288" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E288" t="str">
+        <v>0,86</v>
+      </c>
+      <c r="F288" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G288" t="str">
+        <v>w</v>
+      </c>
+      <c r="H288">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>15</v>
+      </c>
+      <c r="B289" s="1">
+        <v>44575.041666666664</v>
+      </c>
+      <c r="C289" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D289" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E289" t="str">
+        <v>86,4</v>
+      </c>
+      <c r="F289" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G289" t="str">
+        <v>w</v>
+      </c>
+      <c r="H289">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>15</v>
+      </c>
+      <c r="B290" s="1">
+        <v>44762.083333333336</v>
+      </c>
+      <c r="C290" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D290" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E290" t="str">
+        <v>0,86</v>
+      </c>
+      <c r="F290" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G290" t="str">
+        <v>w</v>
+      </c>
+      <c r="H290">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>15</v>
+      </c>
+      <c r="B291" s="1">
+        <v>44762.083333333336</v>
+      </c>
+      <c r="C291" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D291" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E291" t="str">
+        <v>86,4</v>
+      </c>
+      <c r="F291" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G291" t="str">
+        <v>w</v>
+      </c>
+      <c r="H291">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>15</v>
+      </c>
+      <c r="B292" s="1">
+        <v>44934.041666666664</v>
+      </c>
+      <c r="C292" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D292" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E292" t="str">
+        <v>0,92</v>
+      </c>
+      <c r="F292" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G292" t="str">
+        <v>w</v>
+      </c>
+      <c r="H292">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>15</v>
+      </c>
+      <c r="B293" s="1">
+        <v>44934.041666666664</v>
+      </c>
+      <c r="C293" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D293" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E293" t="str">
+        <v>79,2</v>
+      </c>
+      <c r="F293" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G293" t="str">
+        <v>w</v>
+      </c>
+      <c r="H293">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>15</v>
+      </c>
+      <c r="B294" s="1">
+        <v>45113.083333333336</v>
+      </c>
+      <c r="C294" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D294" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E294" t="str">
+        <v>0,89</v>
+      </c>
+      <c r="F294" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G294" t="str">
+        <v>w</v>
+      </c>
+      <c r="H294">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>15</v>
+      </c>
+      <c r="B295" s="1">
+        <v>45113.083333333336</v>
+      </c>
+      <c r="C295" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D295" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E295" t="str">
+        <v>82,4</v>
+      </c>
+      <c r="F295" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G295" t="str">
+        <v>w</v>
+      </c>
+      <c r="H295">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>15</v>
+      </c>
+      <c r="B296" s="1">
+        <v>45307.041666666664</v>
+      </c>
+      <c r="C296" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D296" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E296" t="str">
+        <v>0,91</v>
+      </c>
+      <c r="F296" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G296" t="str">
+        <v>w</v>
+      </c>
+      <c r="H296">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>15</v>
+      </c>
+      <c r="B297" s="1">
+        <v>45307.041666666664</v>
+      </c>
+      <c r="C297" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D297" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E297" t="str">
+        <v>79,8</v>
+      </c>
+      <c r="F297" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G297" t="str">
+        <v>w</v>
+      </c>
+      <c r="H297">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>15</v>
+      </c>
+      <c r="B298" s="1">
+        <v>45486.083333333336</v>
+      </c>
+      <c r="C298" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D298" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E298" t="str">
+        <v>0,94</v>
+      </c>
+      <c r="F298" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G298" t="str">
+        <v>w</v>
+      </c>
+      <c r="H298">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>15</v>
+      </c>
+      <c r="B299" s="1">
+        <v>45486.083333333336</v>
+      </c>
+      <c r="C299" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D299" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E299" t="str">
+        <v>76,7</v>
+      </c>
+      <c r="F299" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G299" t="str">
+        <v>w</v>
+      </c>
+      <c r="H299">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>16</v>
+      </c>
+      <c r="B300" s="1">
+        <v>44598.041666666664</v>
+      </c>
+      <c r="C300" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D300" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E300" t="str">
+        <v>1,07</v>
+      </c>
+      <c r="F300" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G300" t="str">
+        <v>m</v>
+      </c>
+      <c r="H300">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>16</v>
+      </c>
+      <c r="B301" s="1">
+        <v>44598.041666666664</v>
+      </c>
+      <c r="C301" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D301" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E301" t="str">
+        <v>83,0</v>
+      </c>
+      <c r="F301" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G301" t="str">
+        <v>m</v>
+      </c>
+      <c r="H301">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>16</v>
+      </c>
+      <c r="B302" s="1">
+        <v>44782.083333333336</v>
+      </c>
+      <c r="C302" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D302" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E302" t="str">
+        <v>1,14</v>
+      </c>
+      <c r="F302" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G302" t="str">
+        <v>m</v>
+      </c>
+      <c r="H302">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>16</v>
+      </c>
+      <c r="B303" s="1">
+        <v>44782.083333333336</v>
+      </c>
+      <c r="C303" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D303" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E303" t="str">
+        <v>76,9</v>
+      </c>
+      <c r="F303" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G303" t="str">
+        <v>m</v>
+      </c>
+      <c r="H303">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>16</v>
+      </c>
+      <c r="B304" s="1">
+        <v>44978.041666666664</v>
+      </c>
+      <c r="C304" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D304" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E304" t="str">
+        <v>1,16</v>
+      </c>
+      <c r="F304" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G304" t="str">
+        <v>m</v>
+      </c>
+      <c r="H304">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>16</v>
+      </c>
+      <c r="B305" s="1">
+        <v>44978.041666666664</v>
+      </c>
+      <c r="C305" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D305" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E305" t="str">
+        <v>74,8</v>
+      </c>
+      <c r="F305" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G305" t="str">
+        <v>m</v>
+      </c>
+      <c r="H305">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>16</v>
+      </c>
+      <c r="B306" s="1">
+        <v>45159.083333333336</v>
+      </c>
+      <c r="C306" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D306" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E306" t="str">
+        <v>1,12</v>
+      </c>
+      <c r="F306" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G306" t="str">
+        <v>m</v>
+      </c>
+      <c r="H306">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>16</v>
+      </c>
+      <c r="B307" s="1">
+        <v>45159.083333333336</v>
+      </c>
+      <c r="C307" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D307" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E307" t="str">
+        <v>78,1</v>
+      </c>
+      <c r="F307" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G307" t="str">
+        <v>m</v>
+      </c>
+      <c r="H307">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>16</v>
+      </c>
+      <c r="B308" s="1">
+        <v>45333.041666666664</v>
+      </c>
+      <c r="C308" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D308" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E308" t="str">
+        <v>1,15</v>
+      </c>
+      <c r="F308" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G308" t="str">
+        <v>m</v>
+      </c>
+      <c r="H308">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>16</v>
+      </c>
+      <c r="B309" s="1">
+        <v>45333.041666666664</v>
+      </c>
+      <c r="C309" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D309" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E309" t="str">
+        <v>75,2</v>
+      </c>
+      <c r="F309" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G309" t="str">
+        <v>m</v>
+      </c>
+      <c r="H309">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>16</v>
+      </c>
+      <c r="B310" s="1">
+        <v>45524.083333333336</v>
+      </c>
+      <c r="C310" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D310" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E310" t="str">
+        <v>1,20</v>
+      </c>
+      <c r="F310" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G310" t="str">
+        <v>m</v>
+      </c>
+      <c r="H310">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>16</v>
+      </c>
+      <c r="B311" s="1">
+        <v>45524.083333333336</v>
+      </c>
+      <c r="C311" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D311" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E311" t="str">
+        <v>71,4</v>
+      </c>
+      <c r="F311" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G311" t="str">
+        <v>m</v>
+      </c>
+      <c r="H311">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>16</v>
+      </c>
+      <c r="B312" s="1">
+        <v>45694.041666666664</v>
+      </c>
+      <c r="C312" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D312" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E312" t="str">
+        <v>1,14</v>
+      </c>
+      <c r="F312" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G312" t="str">
+        <v>m</v>
+      </c>
+      <c r="H312">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>16</v>
+      </c>
+      <c r="B313" s="1">
+        <v>45694.041666666664</v>
+      </c>
+      <c r="C313" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D313" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E313" t="str">
+        <v>75,5</v>
+      </c>
+      <c r="F313" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G313" t="str">
+        <v>m</v>
+      </c>
+      <c r="H313">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>16</v>
+      </c>
+      <c r="B314" s="1">
+        <v>45874.083333333336</v>
+      </c>
+      <c r="C314" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D314" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E314" t="str">
+        <v>1,24</v>
+      </c>
+      <c r="F314" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G314" t="str">
+        <v>m</v>
+      </c>
+      <c r="H314">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>16</v>
+      </c>
+      <c r="B315" s="1">
+        <v>45874.083333333336</v>
+      </c>
+      <c r="C315" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D315" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E315" t="str">
+        <v>68,2</v>
+      </c>
+      <c r="F315" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G315" t="str">
+        <v>m</v>
+      </c>
+      <c r="H315">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>17</v>
+      </c>
+      <c r="B316" s="1">
+        <v>44447.083333333336</v>
+      </c>
+      <c r="C316" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D316" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E316" t="str">
+        <v>0,85</v>
+      </c>
+      <c r="F316" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G316" t="str">
+        <v>w</v>
+      </c>
+      <c r="H316">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>17</v>
+      </c>
+      <c r="B317" s="1">
+        <v>44447.083333333336</v>
+      </c>
+      <c r="C317" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D317" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E317" t="str">
+        <v>77,4</v>
+      </c>
+      <c r="F317" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G317" t="str">
+        <v>w</v>
+      </c>
+      <c r="H317">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>17</v>
+      </c>
+      <c r="B318" s="1">
+        <v>44643.041666666664</v>
+      </c>
+      <c r="C318" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D318" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E318" t="str">
+        <v>0,87</v>
+      </c>
+      <c r="F318" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G318" t="str">
+        <v>w</v>
+      </c>
+      <c r="H318">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>17</v>
+      </c>
+      <c r="B319" s="1">
+        <v>44643.041666666664</v>
+      </c>
+      <c r="C319" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D319" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E319" t="str">
+        <v>75,3</v>
+      </c>
+      <c r="F319" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G319" t="str">
+        <v>w</v>
+      </c>
+      <c r="H319">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>17</v>
+      </c>
+      <c r="B320" s="1">
+        <v>44810.083333333336</v>
+      </c>
+      <c r="C320" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D320" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E320" t="str">
+        <v>0,91</v>
+      </c>
+      <c r="F320" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G320" t="str">
+        <v>w</v>
+      </c>
+      <c r="H320">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>17</v>
+      </c>
+      <c r="B321" s="1">
+        <v>44810.083333333336</v>
+      </c>
+      <c r="C321" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D321" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E321" t="str">
+        <v>70,9</v>
+      </c>
+      <c r="F321" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G321" t="str">
+        <v>w</v>
+      </c>
+      <c r="H321">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>17</v>
+      </c>
+      <c r="B322" s="1">
+        <v>44992.041666666664</v>
+      </c>
+      <c r="C322" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D322" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E322" t="str">
+        <v>0,96</v>
+      </c>
+      <c r="F322" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G322" t="str">
+        <v>w</v>
+      </c>
+      <c r="H322">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>17</v>
+      </c>
+      <c r="B323" s="1">
+        <v>44992.041666666664</v>
+      </c>
+      <c r="C323" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D323" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E323" t="str">
+        <v>66,5</v>
+      </c>
+      <c r="F323" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G323" t="str">
+        <v>w</v>
+      </c>
+      <c r="H323">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>17</v>
+      </c>
+      <c r="B324" s="1">
+        <v>45175.083333333336</v>
+      </c>
+      <c r="C324" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D324" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E324" t="str">
+        <v>0,93</v>
+      </c>
+      <c r="F324" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G324" t="str">
+        <v>w</v>
+      </c>
+      <c r="H324">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>17</v>
+      </c>
+      <c r="B325" s="1">
+        <v>45175.083333333336</v>
+      </c>
+      <c r="C325" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D325" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E325" t="str">
+        <v>68,6</v>
+      </c>
+      <c r="F325" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G325" t="str">
+        <v>w</v>
+      </c>
+      <c r="H325">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>17</v>
+      </c>
+      <c r="B326" s="1">
+        <v>45356.041666666664</v>
+      </c>
+      <c r="C326" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D326" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E326" t="str">
+        <v>1,01</v>
+      </c>
+      <c r="F326" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G326" t="str">
+        <v>w</v>
+      </c>
+      <c r="H326">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>17</v>
+      </c>
+      <c r="B327" s="1">
+        <v>45356.041666666664</v>
+      </c>
+      <c r="C327" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D327" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E327" t="str">
+        <v>62,2</v>
+      </c>
+      <c r="F327" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G327" t="str">
+        <v>w</v>
+      </c>
+      <c r="H327">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>17</v>
+      </c>
+      <c r="B328" s="1">
+        <v>45556.083333333336</v>
+      </c>
+      <c r="C328" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D328" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E328" t="str">
+        <v>1,00</v>
+      </c>
+      <c r="F328" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G328" t="str">
+        <v>w</v>
+      </c>
+      <c r="H328">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>17</v>
+      </c>
+      <c r="B329" s="1">
+        <v>45556.083333333336</v>
+      </c>
+      <c r="C329" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D329" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E329" t="str">
+        <v>62,5</v>
+      </c>
+      <c r="F329" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G329" t="str">
+        <v>w</v>
+      </c>
+      <c r="H329">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>17</v>
+      </c>
+      <c r="B330" s="1">
+        <v>45721.041666666664</v>
+      </c>
+      <c r="C330" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D330" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E330" t="str">
+        <v>1,06</v>
+      </c>
+      <c r="F330" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G330" t="str">
+        <v>w</v>
+      </c>
+      <c r="H330">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>17</v>
+      </c>
+      <c r="B331" s="1">
+        <v>45721.041666666664</v>
+      </c>
+      <c r="C331" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D331" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E331" t="str">
+        <v>58,3</v>
+      </c>
+      <c r="F331" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G331" t="str">
+        <v>w</v>
+      </c>
+      <c r="H331">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>18</v>
+      </c>
+      <c r="B332" s="1">
+        <v>44092.083333333336</v>
+      </c>
+      <c r="C332" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D332" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E332" t="str">
+        <v>1,22</v>
+      </c>
+      <c r="F332" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G332" t="str">
+        <v>m</v>
+      </c>
+      <c r="H332">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>18</v>
+      </c>
+      <c r="B333" s="1">
+        <v>44092.083333333336</v>
+      </c>
+      <c r="C333" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D333" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E333" t="str">
+        <v>73,6</v>
+      </c>
+      <c r="F333" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G333" t="str">
+        <v>m</v>
+      </c>
+      <c r="H333">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>18</v>
+      </c>
+      <c r="B334" s="1">
+        <v>44261.041666666664</v>
+      </c>
+      <c r="C334" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D334" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E334" t="str">
+        <v>1,23</v>
+      </c>
+      <c r="F334" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G334" t="str">
+        <v>m</v>
+      </c>
+      <c r="H334">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>18</v>
+      </c>
+      <c r="B335" s="1">
+        <v>44261.041666666664</v>
+      </c>
+      <c r="C335" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D335" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E335" t="str">
+        <v>72,9</v>
+      </c>
+      <c r="F335" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G335" t="str">
+        <v>m</v>
+      </c>
+      <c r="H335">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>18</v>
+      </c>
+      <c r="B336" s="1">
+        <v>44455.083333333336</v>
+      </c>
+      <c r="C336" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D336" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E336" t="str">
+        <v>1,30</v>
+      </c>
+      <c r="F336" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G336" t="str">
+        <v>m</v>
+      </c>
+      <c r="H336">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>18</v>
+      </c>
+      <c r="B337" s="1">
+        <v>44455.083333333336</v>
+      </c>
+      <c r="C337" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D337" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E337" t="str">
+        <v>67,8</v>
+      </c>
+      <c r="F337" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G337" t="str">
+        <v>m</v>
+      </c>
+      <c r="H337">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>18</v>
+      </c>
+      <c r="B338" s="1">
+        <v>44626.041666666664</v>
+      </c>
+      <c r="C338" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D338" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E338" t="str">
+        <v>1,28</v>
+      </c>
+      <c r="F338" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G338" t="str">
+        <v>m</v>
+      </c>
+      <c r="H338">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>18</v>
+      </c>
+      <c r="B339" s="1">
+        <v>44626.041666666664</v>
+      </c>
+      <c r="C339" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D339" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E339" t="str">
+        <v>69,0</v>
+      </c>
+      <c r="F339" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G339" t="str">
+        <v>m</v>
+      </c>
+      <c r="H339">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>18</v>
+      </c>
+      <c r="B340" s="1">
+        <v>44823.083333333336</v>
+      </c>
+      <c r="C340" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D340" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E340" t="str">
+        <v>1,29</v>
+      </c>
+      <c r="F340" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G340" t="str">
+        <v>m</v>
+      </c>
+      <c r="H340">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>18</v>
+      </c>
+      <c r="B341" s="1">
+        <v>44823.083333333336</v>
+      </c>
+      <c r="C341" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D341" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E341" t="str">
+        <v>68,0</v>
+      </c>
+      <c r="F341" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G341" t="str">
+        <v>m</v>
+      </c>
+      <c r="H341">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>18</v>
+      </c>
+      <c r="B342" s="1">
+        <v>45005.041666666664</v>
+      </c>
+      <c r="C342" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D342" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E342" t="str">
+        <v>1,33</v>
+      </c>
+      <c r="F342" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G342" t="str">
+        <v>m</v>
+      </c>
+      <c r="H342">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>18</v>
+      </c>
+      <c r="B343" s="1">
+        <v>45005.041666666664</v>
+      </c>
+      <c r="C343" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D343" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E343" t="str">
+        <v>65,5</v>
+      </c>
+      <c r="F343" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G343" t="str">
+        <v>m</v>
+      </c>
+      <c r="H343">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>18</v>
+      </c>
+      <c r="B344" s="1">
+        <v>45190.083333333336</v>
+      </c>
+      <c r="C344" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D344" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E344" t="str">
+        <v>1,37</v>
+      </c>
+      <c r="F344" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G344" t="str">
+        <v>m</v>
+      </c>
+      <c r="H344">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>18</v>
+      </c>
+      <c r="B345" s="1">
+        <v>45190.083333333336</v>
+      </c>
+      <c r="C345" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D345" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E345" t="str">
+        <v>62,8</v>
+      </c>
+      <c r="F345" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G345" t="str">
+        <v>m</v>
+      </c>
+      <c r="H345">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>18</v>
+      </c>
+      <c r="B346" s="1">
+        <v>45372.041666666664</v>
+      </c>
+      <c r="C346" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D346" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E346" t="str">
+        <v>1,35</v>
+      </c>
+      <c r="F346" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G346" t="str">
+        <v>m</v>
+      </c>
+      <c r="H346">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>18</v>
+      </c>
+      <c r="B347" s="1">
+        <v>45372.041666666664</v>
+      </c>
+      <c r="C347" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D347" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E347" t="str">
+        <v>64,0</v>
+      </c>
+      <c r="F347" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G347" t="str">
+        <v>m</v>
+      </c>
+      <c r="H347">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>19</v>
+      </c>
+      <c r="B348" s="1">
+        <v>43868.041666666664</v>
+      </c>
+      <c r="C348" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D348" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E348" t="str">
+        <v>1,24</v>
+      </c>
+      <c r="F348" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G348" t="str">
+        <v>m</v>
+      </c>
+      <c r="H348">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>19</v>
+      </c>
+      <c r="B349" s="1">
+        <v>43868.041666666664</v>
+      </c>
+      <c r="C349" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D349" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E349" t="str">
+        <v>63,3</v>
+      </c>
+      <c r="F349" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G349" t="str">
+        <v>m</v>
+      </c>
+      <c r="H349">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>19</v>
+      </c>
+      <c r="B350" s="1">
+        <v>44051.083333333336</v>
+      </c>
+      <c r="C350" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D350" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E350" t="str">
+        <v>1,21</v>
+      </c>
+      <c r="F350" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G350" t="str">
+        <v>m</v>
+      </c>
+      <c r="H350">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>19</v>
+      </c>
+      <c r="B351" s="1">
+        <v>44051.083333333336</v>
+      </c>
+      <c r="C351" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D351" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E351" t="str">
+        <v>65,2</v>
+      </c>
+      <c r="F351" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G351" t="str">
+        <v>m</v>
+      </c>
+      <c r="H351">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>19</v>
+      </c>
+      <c r="B352" s="1">
+        <v>44245.041666666664</v>
+      </c>
+      <c r="C352" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D352" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E352" t="str">
+        <v>1,29</v>
+      </c>
+      <c r="F352" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G352" t="str">
+        <v>m</v>
+      </c>
+      <c r="H352">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>19</v>
+      </c>
+      <c r="B353" s="1">
+        <v>44245.041666666664</v>
+      </c>
+      <c r="C353" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D353" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E353" t="str">
+        <v>60,0</v>
+      </c>
+      <c r="F353" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G353" t="str">
+        <v>m</v>
+      </c>
+      <c r="H353">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>19</v>
+      </c>
+      <c r="B354" s="1">
+        <v>44430.083333333336</v>
+      </c>
+      <c r="C354" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D354" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E354" t="str">
+        <v>1,37</v>
+      </c>
+      <c r="F354" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G354" t="str">
+        <v>m</v>
+      </c>
+      <c r="H354">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>19</v>
+      </c>
+      <c r="B355" s="1">
+        <v>44430.083333333336</v>
+      </c>
+      <c r="C355" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D355" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E355" t="str">
+        <v>55,8</v>
+      </c>
+      <c r="F355" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G355" t="str">
+        <v>m</v>
+      </c>
+      <c r="H355">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>19</v>
+      </c>
+      <c r="B356" s="1">
+        <v>44604.041666666664</v>
+      </c>
+      <c r="C356" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D356" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E356" t="str">
+        <v>1,42</v>
+      </c>
+      <c r="F356" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G356" t="str">
+        <v>m</v>
+      </c>
+      <c r="H356">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>19</v>
+      </c>
+      <c r="B357" s="1">
+        <v>44604.041666666664</v>
+      </c>
+      <c r="C357" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D357" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E357" t="str">
+        <v>53,2</v>
+      </c>
+      <c r="F357" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G357" t="str">
+        <v>m</v>
+      </c>
+      <c r="H357">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>19</v>
+      </c>
+      <c r="B358" s="1">
+        <v>44790.083333333336</v>
+      </c>
+      <c r="C358" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D358" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E358" t="str">
+        <v>1,45</v>
+      </c>
+      <c r="F358" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G358" t="str">
+        <v>m</v>
+      </c>
+      <c r="H358">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>19</v>
+      </c>
+      <c r="B359" s="1">
+        <v>44790.083333333336</v>
+      </c>
+      <c r="C359" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D359" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E359" t="str">
+        <v>51,8</v>
+      </c>
+      <c r="F359" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G359" t="str">
+        <v>m</v>
+      </c>
+      <c r="H359">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>19</v>
+      </c>
+      <c r="B360" s="1">
+        <v>44965.041666666664</v>
+      </c>
+      <c r="C360" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D360" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E360" t="str">
+        <v>1,50</v>
+      </c>
+      <c r="F360" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G360" t="str">
+        <v>m</v>
+      </c>
+      <c r="H360">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>19</v>
+      </c>
+      <c r="B361" s="1">
+        <v>44965.041666666664</v>
+      </c>
+      <c r="C361" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D361" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E361" t="str">
+        <v>49,5</v>
+      </c>
+      <c r="F361" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G361" t="str">
+        <v>m</v>
+      </c>
+      <c r="H361">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>19</v>
+      </c>
+      <c r="B362" s="1">
+        <v>45146.083333333336</v>
+      </c>
+      <c r="C362" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D362" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E362" t="str">
+        <v>1,56</v>
+      </c>
+      <c r="F362" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G362" t="str">
+        <v>m</v>
+      </c>
+      <c r="H362">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>19</v>
+      </c>
+      <c r="B363" s="1">
+        <v>45146.083333333336</v>
+      </c>
+      <c r="C363" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D363" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E363" t="str">
+        <v>47,2</v>
+      </c>
+      <c r="F363" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G363" t="str">
+        <v>m</v>
+      </c>
+      <c r="H363">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>20</v>
+      </c>
+      <c r="B364" s="1">
+        <v>44057.083333333336</v>
+      </c>
+      <c r="C364" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D364" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E364" t="str">
+        <v>0,80</v>
+      </c>
+      <c r="F364" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G364" t="str">
+        <v>w</v>
+      </c>
+      <c r="H364">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>20</v>
+      </c>
+      <c r="B365" s="1">
+        <v>44057.083333333336</v>
+      </c>
+      <c r="C365" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D365" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E365" t="str">
+        <v>96,1</v>
+      </c>
+      <c r="F365" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G365" t="str">
+        <v>w</v>
+      </c>
+      <c r="H365">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <v>20</v>
+      </c>
+      <c r="B366" s="1">
+        <v>44242.041666666664</v>
+      </c>
+      <c r="C366" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D366" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E366" t="str">
+        <v>0,90</v>
+      </c>
+      <c r="F366" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G366" t="str">
+        <v>w</v>
+      </c>
+      <c r="H366">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <v>20</v>
+      </c>
+      <c r="B367" s="1">
+        <v>44242.041666666664</v>
+      </c>
+      <c r="C367" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D367" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E367" t="str">
+        <v>83,4</v>
+      </c>
+      <c r="F367" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G367" t="str">
+        <v>w</v>
+      </c>
+      <c r="H367">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <v>20</v>
+      </c>
+      <c r="B368" s="1">
+        <v>44424.083333333336</v>
+      </c>
+      <c r="C368" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D368" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E368" t="str">
+        <v>0,89</v>
+      </c>
+      <c r="F368" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G368" t="str">
+        <v>w</v>
+      </c>
+      <c r="H368">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <v>20</v>
+      </c>
+      <c r="B369" s="1">
+        <v>44424.083333333336</v>
+      </c>
+      <c r="C369" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D369" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E369" t="str">
+        <v>84,0</v>
+      </c>
+      <c r="F369" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G369" t="str">
+        <v>w</v>
+      </c>
+      <c r="H369">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370">
+        <v>20</v>
+      </c>
+      <c r="B370" s="1">
+        <v>44609.041666666664</v>
+      </c>
+      <c r="C370" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D370" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E370" t="str">
+        <v>0,97</v>
+      </c>
+      <c r="F370" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G370" t="str">
+        <v>w</v>
+      </c>
+      <c r="H370">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371">
+        <v>20</v>
+      </c>
+      <c r="B371" s="1">
+        <v>44609.041666666664</v>
+      </c>
+      <c r="C371" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D371" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E371" t="str">
+        <v>75,8</v>
+      </c>
+      <c r="F371" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G371" t="str">
+        <v>w</v>
+      </c>
+      <c r="H371">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372">
+        <v>20</v>
+      </c>
+      <c r="B372" s="1">
+        <v>44783.083333333336</v>
+      </c>
+      <c r="C372" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D372" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E372" t="str">
+        <v>1,04</v>
+      </c>
+      <c r="F372" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G372" t="str">
+        <v>w</v>
+      </c>
+      <c r="H372">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373">
+        <v>20</v>
+      </c>
+      <c r="B373" s="1">
+        <v>44783.083333333336</v>
+      </c>
+      <c r="C373" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D373" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E373" t="str">
+        <v>69,2</v>
+      </c>
+      <c r="F373" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G373" t="str">
+        <v>w</v>
+      </c>
+      <c r="H373">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374">
+        <v>20</v>
+      </c>
+      <c r="B374" s="1">
+        <v>44974.041666666664</v>
+      </c>
+      <c r="C374" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D374" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E374" t="str">
+        <v>1,06</v>
+      </c>
+      <c r="F374" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G374" t="str">
+        <v>w</v>
+      </c>
+      <c r="H374">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375">
+        <v>20</v>
+      </c>
+      <c r="B375" s="1">
+        <v>44974.041666666664</v>
+      </c>
+      <c r="C375" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D375" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E375" t="str">
+        <v>67,7</v>
+      </c>
+      <c r="F375" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G375" t="str">
+        <v>w</v>
+      </c>
+      <c r="H375">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376">
+        <v>20</v>
+      </c>
+      <c r="B376" s="1">
+        <v>45149.083333333336</v>
+      </c>
+      <c r="C376" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D376" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E376" t="str">
+        <v>1,06</v>
+      </c>
+      <c r="F376" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G376" t="str">
+        <v>w</v>
+      </c>
+      <c r="H376">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377">
+        <v>20</v>
+      </c>
+      <c r="B377" s="1">
+        <v>45149.083333333336</v>
+      </c>
+      <c r="C377" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D377" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E377" t="str">
+        <v>67,3</v>
+      </c>
+      <c r="F377" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G377" t="str">
+        <v>w</v>
+      </c>
+      <c r="H377">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378">
+        <v>20</v>
+      </c>
+      <c r="B378" s="1">
+        <v>45333.041666666664</v>
+      </c>
+      <c r="C378" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D378" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E378" t="str">
+        <v>1,17</v>
+      </c>
+      <c r="F378" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G378" t="str">
+        <v>w</v>
+      </c>
+      <c r="H378">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379">
+        <v>20</v>
+      </c>
+      <c r="B379" s="1">
+        <v>45333.041666666664</v>
+      </c>
+      <c r="C379" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D379" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E379" t="str">
+        <v>59,7</v>
+      </c>
+      <c r="F379" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G379" t="str">
+        <v>w</v>
+      </c>
+      <c r="H379">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380">
+        <v>21</v>
+      </c>
+      <c r="B380" s="1">
+        <v>44705.083333333336</v>
+      </c>
+      <c r="C380" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D380" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E380" t="str">
+        <v>0,98</v>
+      </c>
+      <c r="F380" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G380" t="str">
+        <v>m</v>
+      </c>
+      <c r="H380">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381">
+        <v>21</v>
+      </c>
+      <c r="B381" s="1">
+        <v>44705.083333333336</v>
+      </c>
+      <c r="C381" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D381" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E381" t="str">
+        <v>96,9</v>
+      </c>
+      <c r="F381" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G381" t="str">
+        <v>m</v>
+      </c>
+      <c r="H381">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382">
+        <v>21</v>
+      </c>
+      <c r="B382" s="1">
+        <v>44888.041666666664</v>
+      </c>
+      <c r="C382" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D382" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E382" t="str">
+        <v>1,01</v>
+      </c>
+      <c r="F382" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G382" t="str">
+        <v>m</v>
+      </c>
+      <c r="H382">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383">
+        <v>21</v>
+      </c>
+      <c r="B383" s="1">
+        <v>44888.041666666664</v>
+      </c>
+      <c r="C383" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D383" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E383" t="str">
+        <v>93,5</v>
+      </c>
+      <c r="F383" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G383" t="str">
+        <v>m</v>
+      </c>
+      <c r="H383">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384">
+        <v>21</v>
+      </c>
+      <c r="B384" s="1">
+        <v>45053.083333333336</v>
+      </c>
+      <c r="C384" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D384" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E384" t="str">
+        <v>1,05</v>
+      </c>
+      <c r="F384" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G384" t="str">
+        <v>m</v>
+      </c>
+      <c r="H384">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385">
+        <v>21</v>
+      </c>
+      <c r="B385" s="1">
+        <v>45053.083333333336</v>
+      </c>
+      <c r="C385" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D385" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E385" t="str">
+        <v>88,7</v>
+      </c>
+      <c r="F385" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G385" t="str">
+        <v>m</v>
+      </c>
+      <c r="H385">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386">
+        <v>21</v>
+      </c>
+      <c r="B386" s="1">
+        <v>45248.041666666664</v>
+      </c>
+      <c r="C386" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D386" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E386" t="str">
+        <v>1,07</v>
+      </c>
+      <c r="F386" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G386" t="str">
+        <v>m</v>
+      </c>
+      <c r="H386">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387">
+        <v>21</v>
+      </c>
+      <c r="B387" s="1">
+        <v>45248.041666666664</v>
+      </c>
+      <c r="C387" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D387" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E387" t="str">
+        <v>86,7</v>
+      </c>
+      <c r="F387" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G387" t="str">
+        <v>m</v>
+      </c>
+      <c r="H387">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388">
+        <v>21</v>
+      </c>
+      <c r="B388" s="1">
+        <v>45423.083333333336</v>
+      </c>
+      <c r="C388" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D388" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E388" t="str">
+        <v>1,15</v>
+      </c>
+      <c r="F388" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G388" t="str">
+        <v>m</v>
+      </c>
+      <c r="H388">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389">
+        <v>21</v>
+      </c>
+      <c r="B389" s="1">
+        <v>45423.083333333336</v>
+      </c>
+      <c r="C389" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D389" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E389" t="str">
+        <v>79,0</v>
+      </c>
+      <c r="F389" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G389" t="str">
+        <v>m</v>
+      </c>
+      <c r="H389">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390">
+        <v>21</v>
+      </c>
+      <c r="B390" s="1">
+        <v>45610.041666666664</v>
+      </c>
+      <c r="C390" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D390" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E390" t="str">
+        <v>1,17</v>
+      </c>
+      <c r="F390" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G390" t="str">
+        <v>m</v>
+      </c>
+      <c r="H390">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391">
+        <v>21</v>
+      </c>
+      <c r="B391" s="1">
+        <v>45610.041666666664</v>
+      </c>
+      <c r="C391" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D391" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E391" t="str">
+        <v>77,4</v>
+      </c>
+      <c r="F391" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G391" t="str">
+        <v>m</v>
+      </c>
+      <c r="H391">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392">
+        <v>21</v>
+      </c>
+      <c r="B392" s="1">
+        <v>45799.083333333336</v>
+      </c>
+      <c r="C392" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D392" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E392" t="str">
+        <v>1,27</v>
+      </c>
+      <c r="F392" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G392" t="str">
+        <v>m</v>
+      </c>
+      <c r="H392">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393">
+        <v>21</v>
+      </c>
+      <c r="B393" s="1">
+        <v>45799.083333333336</v>
+      </c>
+      <c r="C393" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D393" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E393" t="str">
+        <v>69,7</v>
+      </c>
+      <c r="F393" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G393" t="str">
+        <v>m</v>
+      </c>
+      <c r="H393">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394">
+        <v>21</v>
+      </c>
+      <c r="B394" s="1">
+        <v>45968.041666666664</v>
+      </c>
+      <c r="C394" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D394" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E394" t="str">
+        <v>1,32</v>
+      </c>
+      <c r="F394" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G394" t="str">
+        <v>m</v>
+      </c>
+      <c r="H394">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395">
+        <v>21</v>
+      </c>
+      <c r="B395" s="1">
+        <v>45968.041666666664</v>
+      </c>
+      <c r="C395" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D395" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E395" t="str">
+        <v>66,5</v>
+      </c>
+      <c r="F395" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G395" t="str">
+        <v>m</v>
+      </c>
+      <c r="H395">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396">
+        <v>22</v>
+      </c>
+      <c r="B396" s="1">
+        <v>44186.041666666664</v>
+      </c>
+      <c r="C396" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D396" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E396" t="str">
+        <v>0,91</v>
+      </c>
+      <c r="F396" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G396" t="str">
+        <v>w</v>
+      </c>
+      <c r="H396">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397">
+        <v>22</v>
+      </c>
+      <c r="B397" s="1">
+        <v>44186.041666666664</v>
+      </c>
+      <c r="C397" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D397" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E397" t="str">
+        <v>73,6</v>
+      </c>
+      <c r="F397" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G397" t="str">
+        <v>w</v>
+      </c>
+      <c r="H397">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398">
+        <v>22</v>
+      </c>
+      <c r="B398" s="1">
+        <v>44356.083333333336</v>
+      </c>
+      <c r="C398" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D398" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E398" t="str">
+        <v>0,94</v>
+      </c>
+      <c r="F398" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G398" t="str">
+        <v>w</v>
+      </c>
+      <c r="H398">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399">
+        <v>22</v>
+      </c>
+      <c r="B399" s="1">
+        <v>44356.083333333336</v>
+      </c>
+      <c r="C399" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D399" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E399" t="str">
+        <v>70,8</v>
+      </c>
+      <c r="F399" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G399" t="str">
+        <v>w</v>
+      </c>
+      <c r="H399">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400">
+        <v>22</v>
+      </c>
+      <c r="B400" s="1">
+        <v>44542.041666666664</v>
+      </c>
+      <c r="C400" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D400" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E400" t="str">
+        <v>0,97</v>
+      </c>
+      <c r="F400" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G400" t="str">
+        <v>w</v>
+      </c>
+      <c r="H400">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401">
+        <v>22</v>
+      </c>
+      <c r="B401" s="1">
+        <v>44542.041666666664</v>
+      </c>
+      <c r="C401" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D401" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E401" t="str">
+        <v>67,7</v>
+      </c>
+      <c r="F401" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G401" t="str">
+        <v>w</v>
+      </c>
+      <c r="H401">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402">
+        <v>22</v>
+      </c>
+      <c r="B402" s="1">
+        <v>44720.083333333336</v>
+      </c>
+      <c r="C402" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D402" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E402" t="str">
+        <v>0,96</v>
+      </c>
+      <c r="F402" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G402" t="str">
+        <v>w</v>
+      </c>
+      <c r="H402">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403">
+        <v>22</v>
+      </c>
+      <c r="B403" s="1">
+        <v>44720.083333333336</v>
+      </c>
+      <c r="C403" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D403" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E403" t="str">
+        <v>68,6</v>
+      </c>
+      <c r="F403" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G403" t="str">
+        <v>w</v>
+      </c>
+      <c r="H403">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404">
+        <v>22</v>
+      </c>
+      <c r="B404" s="1">
+        <v>44901.041666666664</v>
+      </c>
+      <c r="C404" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D404" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E404" t="str">
+        <v>0,98</v>
+      </c>
+      <c r="F404" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G404" t="str">
+        <v>w</v>
+      </c>
+      <c r="H404">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405">
+        <v>22</v>
+      </c>
+      <c r="B405" s="1">
+        <v>44901.041666666664</v>
+      </c>
+      <c r="C405" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D405" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E405" t="str">
+        <v>66,5</v>
+      </c>
+      <c r="F405" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G405" t="str">
+        <v>w</v>
+      </c>
+      <c r="H405">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406">
+        <v>22</v>
+      </c>
+      <c r="B406" s="1">
+        <v>45087.083333333336</v>
+      </c>
+      <c r="C406" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D406" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E406" t="str">
+        <v>1,04</v>
+      </c>
+      <c r="F406" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G406" t="str">
+        <v>w</v>
+      </c>
+      <c r="H406">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407">
+        <v>22</v>
+      </c>
+      <c r="B407" s="1">
+        <v>45087.083333333336</v>
+      </c>
+      <c r="C407" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D407" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E407" t="str">
+        <v>61,9</v>
+      </c>
+      <c r="F407" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G407" t="str">
+        <v>w</v>
+      </c>
+      <c r="H407">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408">
+        <v>22</v>
+      </c>
+      <c r="B408" s="1">
+        <v>45273.041666666664</v>
+      </c>
+      <c r="C408" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D408" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E408" t="str">
+        <v>1,10</v>
+      </c>
+      <c r="F408" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G408" t="str">
+        <v>w</v>
+      </c>
+      <c r="H408">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409">
+        <v>22</v>
+      </c>
+      <c r="B409" s="1">
+        <v>45273.041666666664</v>
+      </c>
+      <c r="C409" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D409" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E409" t="str">
+        <v>57,5</v>
+      </c>
+      <c r="F409" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G409" t="str">
+        <v>w</v>
+      </c>
+      <c r="H409">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410">
+        <v>22</v>
+      </c>
+      <c r="B410" s="1">
+        <v>45462.083333333336</v>
+      </c>
+      <c r="C410" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D410" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E410" t="str">
+        <v>1,16</v>
+      </c>
+      <c r="F410" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G410" t="str">
+        <v>w</v>
+      </c>
+      <c r="H410">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411">
+        <v>22</v>
+      </c>
+      <c r="B411" s="1">
+        <v>45462.083333333336</v>
+      </c>
+      <c r="C411" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D411" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E411" t="str">
+        <v>54,0</v>
+      </c>
+      <c r="F411" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G411" t="str">
+        <v>w</v>
+      </c>
+      <c r="H411">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412">
+        <v>23</v>
+      </c>
+      <c r="B412" s="1">
+        <v>44881.041666666664</v>
+      </c>
+      <c r="C412" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D412" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E412" t="str">
+        <v>1,20</v>
+      </c>
+      <c r="F412" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G412" t="str">
+        <v>m</v>
+      </c>
+      <c r="H412">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413">
+        <v>23</v>
+      </c>
+      <c r="B413" s="1">
+        <v>44881.041666666664</v>
+      </c>
+      <c r="C413" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D413" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E413" t="str">
+        <v>73,7</v>
+      </c>
+      <c r="F413" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G413" t="str">
+        <v>m</v>
+      </c>
+      <c r="H413">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414">
+        <v>23</v>
+      </c>
+      <c r="B414" s="1">
+        <v>45059.083333333336</v>
+      </c>
+      <c r="C414" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D414" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E414" t="str">
+        <v>1,28</v>
+      </c>
+      <c r="F414" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G414" t="str">
+        <v>m</v>
+      </c>
+      <c r="H414">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415">
+        <v>23</v>
+      </c>
+      <c r="B415" s="1">
+        <v>45059.083333333336</v>
+      </c>
+      <c r="C415" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D415" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E415" t="str">
+        <v>68,2</v>
+      </c>
+      <c r="F415" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G415" t="str">
+        <v>m</v>
+      </c>
+      <c r="H415">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416">
+        <v>23</v>
+      </c>
+      <c r="B416" s="1">
+        <v>45249.041666666664</v>
+      </c>
+      <c r="C416" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D416" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E416" t="str">
+        <v>1,26</v>
+      </c>
+      <c r="F416" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G416" t="str">
+        <v>m</v>
+      </c>
+      <c r="H416">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417">
+        <v>23</v>
+      </c>
+      <c r="B417" s="1">
+        <v>45249.041666666664</v>
+      </c>
+      <c r="C417" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D417" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E417" t="str">
+        <v>69,1</v>
+      </c>
+      <c r="F417" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G417" t="str">
+        <v>m</v>
+      </c>
+      <c r="H417">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418">
+        <v>23</v>
+      </c>
+      <c r="B418" s="1">
+        <v>45436.083333333336</v>
+      </c>
+      <c r="C418" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D418" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E418" t="str">
+        <v>1,37</v>
+      </c>
+      <c r="F418" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G418" t="str">
+        <v>m</v>
+      </c>
+      <c r="H418">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419">
+        <v>23</v>
+      </c>
+      <c r="B419" s="1">
+        <v>45436.083333333336</v>
+      </c>
+      <c r="C419" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D419" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E419" t="str">
+        <v>62,5</v>
+      </c>
+      <c r="F419" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G419" t="str">
+        <v>m</v>
+      </c>
+      <c r="H419">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420">
+        <v>23</v>
+      </c>
+      <c r="B420" s="1">
+        <v>45602.041666666664</v>
+      </c>
+      <c r="C420" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D420" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E420" t="str">
+        <v>1,42</v>
+      </c>
+      <c r="F420" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G420" t="str">
+        <v>m</v>
+      </c>
+      <c r="H420">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421">
+        <v>23</v>
+      </c>
+      <c r="B421" s="1">
+        <v>45602.041666666664</v>
+      </c>
+      <c r="C421" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D421" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E421" t="str">
+        <v>59,5</v>
+      </c>
+      <c r="F421" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G421" t="str">
+        <v>m</v>
+      </c>
+      <c r="H421">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422">
+        <v>23</v>
+      </c>
+      <c r="B422" s="1">
+        <v>45790.083333333336</v>
+      </c>
+      <c r="C422" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D422" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E422" t="str">
+        <v>1,36</v>
+      </c>
+      <c r="F422" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G422" t="str">
+        <v>m</v>
+      </c>
+      <c r="H422">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423">
+        <v>23</v>
+      </c>
+      <c r="B423" s="1">
+        <v>45790.083333333336</v>
+      </c>
+      <c r="C423" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D423" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E423" t="str">
+        <v>62,6</v>
+      </c>
+      <c r="F423" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G423" t="str">
+        <v>m</v>
+      </c>
+      <c r="H423">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424">
+        <v>23</v>
+      </c>
+      <c r="B424" s="1">
+        <v>45971.041666666664</v>
+      </c>
+      <c r="C424" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D424" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E424" t="str">
+        <v>1,44</v>
+      </c>
+      <c r="F424" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G424" t="str">
+        <v>m</v>
+      </c>
+      <c r="H424">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425">
+        <v>23</v>
+      </c>
+      <c r="B425" s="1">
+        <v>45971.041666666664</v>
+      </c>
+      <c r="C425" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D425" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E425" t="str">
+        <v>58,1</v>
+      </c>
+      <c r="F425" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G425" t="str">
+        <v>m</v>
+      </c>
+      <c r="H425">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426">
+        <v>23</v>
+      </c>
+      <c r="B426" s="1">
+        <v>46164.083333333336</v>
+      </c>
+      <c r="C426" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D426" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E426" t="str">
+        <v>1,50</v>
+      </c>
+      <c r="F426" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G426" t="str">
+        <v>m</v>
+      </c>
+      <c r="H426">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427">
+        <v>23</v>
+      </c>
+      <c r="B427" s="1">
+        <v>46164.083333333336</v>
+      </c>
+      <c r="C427" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D427" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E427" t="str">
+        <v>55,3</v>
+      </c>
+      <c r="F427" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G427" t="str">
+        <v>m</v>
+      </c>
+      <c r="H427">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428">
+        <v>24</v>
+      </c>
+      <c r="B428" s="1">
+        <v>44873.041666666664</v>
+      </c>
+      <c r="C428" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D428" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E428" t="str">
+        <v>0,78</v>
+      </c>
+      <c r="F428" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G428" t="str">
+        <v>w</v>
+      </c>
+      <c r="H428">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429">
+        <v>24</v>
+      </c>
+      <c r="B429" s="1">
+        <v>44873.041666666664</v>
+      </c>
+      <c r="C429" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D429" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E429" t="str">
+        <v>84,8</v>
+      </c>
+      <c r="F429" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G429" t="str">
+        <v>w</v>
+      </c>
+      <c r="H429">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430">
+        <v>24</v>
+      </c>
+      <c r="B430" s="1">
+        <v>45064.083333333336</v>
+      </c>
+      <c r="C430" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D430" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E430" t="str">
+        <v>0,76</v>
+      </c>
+      <c r="F430" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G430" t="str">
+        <v>w</v>
+      </c>
+      <c r="H430">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431">
+        <v>24</v>
+      </c>
+      <c r="B431" s="1">
+        <v>45064.083333333336</v>
+      </c>
+      <c r="C431" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D431" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E431" t="str">
+        <v>87,4</v>
+      </c>
+      <c r="F431" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G431" t="str">
+        <v>w</v>
+      </c>
+      <c r="H431">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432">
+        <v>24</v>
+      </c>
+      <c r="B432" s="1">
+        <v>45241.041666666664</v>
+      </c>
+      <c r="C432" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D432" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E432" t="str">
+        <v>0,81</v>
+      </c>
+      <c r="F432" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G432" t="str">
+        <v>w</v>
+      </c>
+      <c r="H432">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433">
+        <v>24</v>
+      </c>
+      <c r="B433" s="1">
+        <v>45241.041666666664</v>
+      </c>
+      <c r="C433" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D433" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E433" t="str">
+        <v>80,5</v>
+      </c>
+      <c r="F433" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G433" t="str">
+        <v>w</v>
+      </c>
+      <c r="H433">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434">
+        <v>24</v>
+      </c>
+      <c r="B434" s="1">
+        <v>45436.083333333336</v>
+      </c>
+      <c r="C434" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D434" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E434" t="str">
+        <v>0,91</v>
+      </c>
+      <c r="F434" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G434" t="str">
+        <v>w</v>
+      </c>
+      <c r="H434">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435">
+        <v>24</v>
+      </c>
+      <c r="B435" s="1">
+        <v>45436.083333333336</v>
+      </c>
+      <c r="C435" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D435" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E435" t="str">
+        <v>70,0</v>
+      </c>
+      <c r="F435" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G435" t="str">
+        <v>w</v>
+      </c>
+      <c r="H435">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436">
+        <v>24</v>
+      </c>
+      <c r="B436" s="1">
+        <v>45614.041666666664</v>
+      </c>
+      <c r="C436" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D436" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E436" t="str">
+        <v>0,90</v>
+      </c>
+      <c r="F436" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G436" t="str">
+        <v>w</v>
+      </c>
+      <c r="H436">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437">
+        <v>24</v>
+      </c>
+      <c r="B437" s="1">
+        <v>45614.041666666664</v>
+      </c>
+      <c r="C437" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D437" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E437" t="str">
+        <v>70,5</v>
+      </c>
+      <c r="F437" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G437" t="str">
+        <v>w</v>
+      </c>
+      <c r="H437">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438">
+        <v>24</v>
+      </c>
+      <c r="B438" s="1">
+        <v>45788.083333333336</v>
+      </c>
+      <c r="C438" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D438" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E438" t="str">
+        <v>0,99</v>
+      </c>
+      <c r="F438" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G438" t="str">
+        <v>w</v>
+      </c>
+      <c r="H438">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439">
+        <v>24</v>
+      </c>
+      <c r="B439" s="1">
+        <v>45788.083333333336</v>
+      </c>
+      <c r="C439" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D439" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E439" t="str">
+        <v>62,9</v>
+      </c>
+      <c r="F439" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G439" t="str">
+        <v>w</v>
+      </c>
+      <c r="H439">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440">
+        <v>24</v>
+      </c>
+      <c r="B440" s="1">
+        <v>45973.041666666664</v>
+      </c>
+      <c r="C440" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D440" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E440" t="str">
+        <v>1,06</v>
+      </c>
+      <c r="F440" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G440" t="str">
+        <v>w</v>
+      </c>
+      <c r="H440">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441">
+        <v>24</v>
+      </c>
+      <c r="B441" s="1">
+        <v>45973.041666666664</v>
+      </c>
+      <c r="C441" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D441" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E441" t="str">
+        <v>57,6</v>
+      </c>
+      <c r="F441" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G441" t="str">
+        <v>w</v>
+      </c>
+      <c r="H441">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442">
+        <v>24</v>
+      </c>
+      <c r="B442" s="1">
+        <v>46160.083333333336</v>
+      </c>
+      <c r="C442" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D442" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E442" t="str">
+        <v>1,10</v>
+      </c>
+      <c r="F442" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G442" t="str">
+        <v>w</v>
+      </c>
+      <c r="H442">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443">
+        <v>24</v>
+      </c>
+      <c r="B443" s="1">
+        <v>46160.083333333336</v>
+      </c>
+      <c r="C443" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D443" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E443" t="str">
+        <v>55,1</v>
+      </c>
+      <c r="F443" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G443" t="str">
+        <v>w</v>
+      </c>
+      <c r="H443">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444">
+        <v>25</v>
+      </c>
+      <c r="B444" s="1">
+        <v>44626.041666666664</v>
+      </c>
+      <c r="C444" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D444" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E444" t="str">
+        <v>0,98</v>
+      </c>
+      <c r="F444" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G444" t="str">
+        <v>w</v>
+      </c>
+      <c r="H444">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445">
+        <v>25</v>
+      </c>
+      <c r="B445" s="1">
+        <v>44626.041666666664</v>
+      </c>
+      <c r="C445" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D445" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E445" t="str">
+        <v>76,7</v>
+      </c>
+      <c r="F445" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G445" t="str">
+        <v>w</v>
+      </c>
+      <c r="H445">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446">
+        <v>25</v>
+      </c>
+      <c r="B446" s="1">
+        <v>44814.083333333336</v>
+      </c>
+      <c r="C446" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D446" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E446" t="str">
+        <v>1,02</v>
+      </c>
+      <c r="F446" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G446" t="str">
+        <v>w</v>
+      </c>
+      <c r="H446">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447">
+        <v>25</v>
+      </c>
+      <c r="B447" s="1">
+        <v>44814.083333333336</v>
+      </c>
+      <c r="C447" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D447" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E447" t="str">
+        <v>73,1</v>
+      </c>
+      <c r="F447" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G447" t="str">
+        <v>w</v>
+      </c>
+      <c r="H447">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448">
+        <v>25</v>
+      </c>
+      <c r="B448" s="1">
+        <v>45000.041666666664</v>
+      </c>
+      <c r="C448" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D448" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E448" t="str">
+        <v>1,07</v>
+      </c>
+      <c r="F448" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G448" t="str">
+        <v>w</v>
+      </c>
+      <c r="H448">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449">
+        <v>25</v>
+      </c>
+      <c r="B449" s="1">
+        <v>45000.041666666664</v>
+      </c>
+      <c r="C449" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D449" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E449" t="str">
+        <v>68,6</v>
+      </c>
+      <c r="F449" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G449" t="str">
+        <v>w</v>
+      </c>
+      <c r="H449">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450">
+        <v>25</v>
+      </c>
+      <c r="B450" s="1">
+        <v>45176.083333333336</v>
+      </c>
+      <c r="C450" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D450" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E450" t="str">
+        <v>1,19</v>
+      </c>
+      <c r="F450" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G450" t="str">
+        <v>w</v>
+      </c>
+      <c r="H450">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451">
+        <v>25</v>
+      </c>
+      <c r="B451" s="1">
+        <v>45176.083333333336</v>
+      </c>
+      <c r="C451" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D451" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E451" t="str">
+        <v>60,4</v>
+      </c>
+      <c r="F451" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G451" t="str">
+        <v>w</v>
+      </c>
+      <c r="H451">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452">
+        <v>25</v>
+      </c>
+      <c r="B452" s="1">
+        <v>45357.041666666664</v>
+      </c>
+      <c r="C452" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D452" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E452" t="str">
+        <v>1,19</v>
+      </c>
+      <c r="F452" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G452" t="str">
+        <v>w</v>
+      </c>
+      <c r="H452">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453">
+        <v>25</v>
+      </c>
+      <c r="B453" s="1">
+        <v>45357.041666666664</v>
+      </c>
+      <c r="C453" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D453" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E453" t="str">
+        <v>60,0</v>
+      </c>
+      <c r="F453" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G453" t="str">
+        <v>w</v>
+      </c>
+      <c r="H453">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454">
+        <v>25</v>
+      </c>
+      <c r="B454" s="1">
+        <v>45554.083333333336</v>
+      </c>
+      <c r="C454" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D454" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E454" t="str">
+        <v>1,29</v>
+      </c>
+      <c r="F454" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G454" t="str">
+        <v>w</v>
+      </c>
+      <c r="H454">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455">
+        <v>25</v>
+      </c>
+      <c r="B455" s="1">
+        <v>45554.083333333336</v>
+      </c>
+      <c r="C455" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D455" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E455" t="str">
+        <v>54,5</v>
+      </c>
+      <c r="F455" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G455" t="str">
+        <v>w</v>
+      </c>
+      <c r="H455">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456">
+        <v>25</v>
+      </c>
+      <c r="B456" s="1">
+        <v>45727.041666666664</v>
+      </c>
+      <c r="C456" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D456" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E456" t="str">
+        <v>1,33</v>
+      </c>
+      <c r="F456" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G456" t="str">
+        <v>w</v>
+      </c>
+      <c r="H456">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457">
+        <v>25</v>
+      </c>
+      <c r="B457" s="1">
+        <v>45727.041666666664</v>
+      </c>
+      <c r="C457" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D457" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E457" t="str">
+        <v>52,2</v>
+      </c>
+      <c r="F457" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G457" t="str">
+        <v>w</v>
+      </c>
+      <c r="H457">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458">
+        <v>25</v>
+      </c>
+      <c r="B458" s="1">
+        <v>45919.083333333336</v>
+      </c>
+      <c r="C458" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D458" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E458" t="str">
+        <v>1,45</v>
+      </c>
+      <c r="F458" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G458" t="str">
+        <v>w</v>
+      </c>
+      <c r="H458">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459">
+        <v>25</v>
+      </c>
+      <c r="B459" s="1">
+        <v>45919.083333333336</v>
+      </c>
+      <c r="C459" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D459" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E459" t="str">
+        <v>47,1</v>
+      </c>
+      <c r="F459" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G459" t="str">
+        <v>w</v>
+      </c>
+      <c r="H459">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460">
+        <v>26</v>
+      </c>
+      <c r="B460" s="1">
+        <v>44006.083333333336</v>
+      </c>
+      <c r="C460" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D460" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E460" t="str">
+        <v>1,06</v>
+      </c>
+      <c r="F460" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G460" t="str">
+        <v>m</v>
+      </c>
+      <c r="H460">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461">
+        <v>26</v>
+      </c>
+      <c r="B461" s="1">
+        <v>44006.083333333336</v>
+      </c>
+      <c r="C461" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D461" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E461" t="str">
+        <v>80,8</v>
+      </c>
+      <c r="F461" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G461" t="str">
+        <v>m</v>
+      </c>
+      <c r="H461">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462">
+        <v>26</v>
+      </c>
+      <c r="B462" s="1">
+        <v>44175.041666666664</v>
+      </c>
+      <c r="C462" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D462" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E462" t="str">
+        <v>1,10</v>
+      </c>
+      <c r="F462" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G462" t="str">
+        <v>m</v>
+      </c>
+      <c r="H462">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463">
+        <v>26</v>
+      </c>
+      <c r="B463" s="1">
+        <v>44175.041666666664</v>
+      </c>
+      <c r="C463" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D463" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E463" t="str">
+        <v>77,3</v>
+      </c>
+      <c r="F463" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G463" t="str">
+        <v>m</v>
+      </c>
+      <c r="H463">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464">
+        <v>26</v>
+      </c>
+      <c r="B464" s="1">
+        <v>44353.083333333336</v>
+      </c>
+      <c r="C464" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D464" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E464" t="str">
+        <v>1,18</v>
+      </c>
+      <c r="F464" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G464" t="str">
+        <v>m</v>
+      </c>
+      <c r="H464">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465">
+        <v>26</v>
+      </c>
+      <c r="B465" s="1">
+        <v>44353.083333333336</v>
+      </c>
+      <c r="C465" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D465" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E465" t="str">
+        <v>70,6</v>
+      </c>
+      <c r="F465" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G465" t="str">
+        <v>m</v>
+      </c>
+      <c r="H465">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466">
+        <v>26</v>
+      </c>
+      <c r="B466" s="1">
+        <v>44541.041666666664</v>
+      </c>
+      <c r="C466" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D466" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E466" t="str">
+        <v>1,24</v>
+      </c>
+      <c r="F466" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G466" t="str">
+        <v>m</v>
+      </c>
+      <c r="H466">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467">
+        <v>26</v>
+      </c>
+      <c r="B467" s="1">
+        <v>44541.041666666664</v>
+      </c>
+      <c r="C467" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D467" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E467" t="str">
+        <v>66,6</v>
+      </c>
+      <c r="F467" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G467" t="str">
+        <v>m</v>
+      </c>
+      <c r="H467">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468">
+        <v>26</v>
+      </c>
+      <c r="B468" s="1">
+        <v>44728.083333333336</v>
+      </c>
+      <c r="C468" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D468" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E468" t="str">
+        <v>1,30</v>
+      </c>
+      <c r="F468" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G468" t="str">
+        <v>m</v>
+      </c>
+      <c r="H468">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469">
+        <v>26</v>
+      </c>
+      <c r="B469" s="1">
+        <v>44728.083333333336</v>
+      </c>
+      <c r="C469" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D469" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E469" t="str">
+        <v>62,5</v>
+      </c>
+      <c r="F469" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G469" t="str">
+        <v>m</v>
+      </c>
+      <c r="H469">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470">
+        <v>26</v>
+      </c>
+      <c r="B470" s="1">
+        <v>44906.041666666664</v>
+      </c>
+      <c r="C470" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D470" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E470" t="str">
+        <v>1,43</v>
+      </c>
+      <c r="F470" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G470" t="str">
+        <v>m</v>
+      </c>
+      <c r="H470">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471">
+        <v>26</v>
+      </c>
+      <c r="B471" s="1">
+        <v>44906.041666666664</v>
+      </c>
+      <c r="C471" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D471" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E471" t="str">
+        <v>55,7</v>
+      </c>
+      <c r="F471" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G471" t="str">
+        <v>m</v>
+      </c>
+      <c r="H471">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472">
+        <v>26</v>
+      </c>
+      <c r="B472" s="1">
+        <v>45090.083333333336</v>
+      </c>
+      <c r="C472" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D472" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E472" t="str">
+        <v>1,53</v>
+      </c>
+      <c r="F472" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G472" t="str">
+        <v>m</v>
+      </c>
+      <c r="H472">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473">
+        <v>26</v>
+      </c>
+      <c r="B473" s="1">
+        <v>45090.083333333336</v>
+      </c>
+      <c r="C473" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D473" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E473" t="str">
+        <v>51,1</v>
+      </c>
+      <c r="F473" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G473" t="str">
+        <v>m</v>
+      </c>
+      <c r="H473">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474">
+        <v>26</v>
+      </c>
+      <c r="B474" s="1">
+        <v>45282.041666666664</v>
+      </c>
+      <c r="C474" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D474" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E474" t="str">
+        <v>1,62</v>
+      </c>
+      <c r="F474" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G474" t="str">
+        <v>m</v>
+      </c>
+      <c r="H474">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475">
+        <v>26</v>
+      </c>
+      <c r="B475" s="1">
+        <v>45282.041666666664</v>
+      </c>
+      <c r="C475" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D475" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E475" t="str">
+        <v>47,7</v>
+      </c>
+      <c r="F475" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G475" t="str">
+        <v>m</v>
+      </c>
+      <c r="H475">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H283"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H475"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7863,7 +12855,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7985,9 +12977,233 @@
         <v>C</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" t="str">
+        <v>UMOD</v>
+      </c>
+      <c r="C10" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D10" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="str">
+        <v>UMOD</v>
+      </c>
+      <c r="C11" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D11" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MUC1</v>
+      </c>
+      <c r="C12" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D12" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13" t="str">
+        <v>PKD1</v>
+      </c>
+      <c r="C13" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D13" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>15</v>
+      </c>
+      <c r="B14" t="str">
+        <v>UMOD</v>
+      </c>
+      <c r="C14" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D14" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>16</v>
+      </c>
+      <c r="B15" t="str">
+        <v>UMOD</v>
+      </c>
+      <c r="C15" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D15" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>17</v>
+      </c>
+      <c r="B16" t="str">
+        <v>UMOD</v>
+      </c>
+      <c r="C16" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D16" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>18</v>
+      </c>
+      <c r="B17" t="str">
+        <v>UMOD</v>
+      </c>
+      <c r="C17" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D17" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>19</v>
+      </c>
+      <c r="B18" t="str">
+        <v>UMOD</v>
+      </c>
+      <c r="C18" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D18" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>20</v>
+      </c>
+      <c r="B19" t="str">
+        <v>MUC1</v>
+      </c>
+      <c r="C19" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D19" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>21</v>
+      </c>
+      <c r="B20" t="str">
+        <v>PKD1</v>
+      </c>
+      <c r="C20" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D20" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>22</v>
+      </c>
+      <c r="B21" t="str">
+        <v>MUC1</v>
+      </c>
+      <c r="C21" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D21" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>23</v>
+      </c>
+      <c r="B22" t="str">
+        <v>PKD1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D22" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>24</v>
+      </c>
+      <c r="B23" t="str">
+        <v>MUC1</v>
+      </c>
+      <c r="C23" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D23" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>25</v>
+      </c>
+      <c r="B24" t="str">
+        <v>PKD1</v>
+      </c>
+      <c r="C24" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D24" t="str">
+        <v>B</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>26</v>
+      </c>
+      <c r="B25" t="str">
+        <v>MUC1</v>
+      </c>
+      <c r="C25" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D25" t="str">
+        <v>B</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/test_labs.xlsx
+++ b/public/test_labs.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H475"/>
+  <dimension ref="A1:H507"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -12667,9 +12667,841 @@
         <v>62</v>
       </c>
     </row>
+    <row r="476">
+      <c r="A476">
+        <v>27</v>
+      </c>
+      <c r="B476" s="1">
+        <v>44659.083333333336</v>
+      </c>
+      <c r="C476" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D476" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E476" t="str">
+        <v>0,91</v>
+      </c>
+      <c r="F476" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G476" t="str">
+        <v>w</v>
+      </c>
+      <c r="H476">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477">
+        <v>27</v>
+      </c>
+      <c r="B477" s="1">
+        <v>44659.083333333336</v>
+      </c>
+      <c r="C477" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D477" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E477" t="str">
+        <v>77,3</v>
+      </c>
+      <c r="F477" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G477" t="str">
+        <v>w</v>
+      </c>
+      <c r="H477">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478">
+        <v>27</v>
+      </c>
+      <c r="B478" s="1">
+        <v>44850.083333333336</v>
+      </c>
+      <c r="C478" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D478" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E478" t="str">
+        <v>0,89</v>
+      </c>
+      <c r="F478" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G478" t="str">
+        <v>w</v>
+      </c>
+      <c r="H478">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479">
+        <v>27</v>
+      </c>
+      <c r="B479" s="1">
+        <v>44850.083333333336</v>
+      </c>
+      <c r="C479" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D479" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E479" t="str">
+        <v>79,4</v>
+      </c>
+      <c r="F479" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G479" t="str">
+        <v>w</v>
+      </c>
+      <c r="H479">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480">
+        <v>27</v>
+      </c>
+      <c r="B480" s="1">
+        <v>45035.083333333336</v>
+      </c>
+      <c r="C480" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D480" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E480" t="str">
+        <v>0,96</v>
+      </c>
+      <c r="F480" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G480" t="str">
+        <v>w</v>
+      </c>
+      <c r="H480">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481">
+        <v>27</v>
+      </c>
+      <c r="B481" s="1">
+        <v>45035.083333333336</v>
+      </c>
+      <c r="C481" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D481" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E481" t="str">
+        <v>72,1</v>
+      </c>
+      <c r="F481" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G481" t="str">
+        <v>w</v>
+      </c>
+      <c r="H481">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482">
+        <v>27</v>
+      </c>
+      <c r="B482" s="1">
+        <v>45220.083333333336</v>
+      </c>
+      <c r="C482" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D482" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E482" t="str">
+        <v>0,95</v>
+      </c>
+      <c r="F482" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G482" t="str">
+        <v>w</v>
+      </c>
+      <c r="H482">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483">
+        <v>27</v>
+      </c>
+      <c r="B483" s="1">
+        <v>45220.083333333336</v>
+      </c>
+      <c r="C483" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D483" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E483" t="str">
+        <v>73,0</v>
+      </c>
+      <c r="F483" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G483" t="str">
+        <v>w</v>
+      </c>
+      <c r="H483">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484">
+        <v>27</v>
+      </c>
+      <c r="B484" s="1">
+        <v>45389.083333333336</v>
+      </c>
+      <c r="C484" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D484" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E484" t="str">
+        <v>0,99</v>
+      </c>
+      <c r="F484" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G484" t="str">
+        <v>w</v>
+      </c>
+      <c r="H484">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485">
+        <v>27</v>
+      </c>
+      <c r="B485" s="1">
+        <v>45389.083333333336</v>
+      </c>
+      <c r="C485" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D485" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E485" t="str">
+        <v>69,0</v>
+      </c>
+      <c r="F485" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G485" t="str">
+        <v>w</v>
+      </c>
+      <c r="H485">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486">
+        <v>27</v>
+      </c>
+      <c r="B486" s="1">
+        <v>45582.083333333336</v>
+      </c>
+      <c r="C486" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D486" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E486" t="str">
+        <v>1,06</v>
+      </c>
+      <c r="F486" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G486" t="str">
+        <v>w</v>
+      </c>
+      <c r="H486">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487">
+        <v>27</v>
+      </c>
+      <c r="B487" s="1">
+        <v>45582.083333333336</v>
+      </c>
+      <c r="C487" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D487" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E487" t="str">
+        <v>63,6</v>
+      </c>
+      <c r="F487" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G487" t="str">
+        <v>w</v>
+      </c>
+      <c r="H487">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488">
+        <v>27</v>
+      </c>
+      <c r="B488" s="1">
+        <v>45762.083333333336</v>
+      </c>
+      <c r="C488" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D488" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E488" t="str">
+        <v>1,06</v>
+      </c>
+      <c r="F488" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G488" t="str">
+        <v>w</v>
+      </c>
+      <c r="H488">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489">
+        <v>27</v>
+      </c>
+      <c r="B489" s="1">
+        <v>45762.083333333336</v>
+      </c>
+      <c r="C489" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D489" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E489" t="str">
+        <v>63,2</v>
+      </c>
+      <c r="F489" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G489" t="str">
+        <v>w</v>
+      </c>
+      <c r="H489">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490">
+        <v>27</v>
+      </c>
+      <c r="B490" s="1">
+        <v>45939.083333333336</v>
+      </c>
+      <c r="C490" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D490" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E490" t="str">
+        <v>1,16</v>
+      </c>
+      <c r="F490" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G490" t="str">
+        <v>w</v>
+      </c>
+      <c r="H490">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491">
+        <v>27</v>
+      </c>
+      <c r="B491" s="1">
+        <v>45939.083333333336</v>
+      </c>
+      <c r="C491" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D491" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E491" t="str">
+        <v>56,7</v>
+      </c>
+      <c r="F491" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G491" t="str">
+        <v>w</v>
+      </c>
+      <c r="H491">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492">
+        <v>28</v>
+      </c>
+      <c r="B492" s="1">
+        <v>43885.041666666664</v>
+      </c>
+      <c r="C492" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D492" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E492" t="str">
+        <v>1,14</v>
+      </c>
+      <c r="F492" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G492" t="str">
+        <v>m</v>
+      </c>
+      <c r="H492">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493">
+        <v>28</v>
+      </c>
+      <c r="B493" s="1">
+        <v>43885.041666666664</v>
+      </c>
+      <c r="C493" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D493" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E493" t="str">
+        <v>75,5</v>
+      </c>
+      <c r="F493" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G493" t="str">
+        <v>m</v>
+      </c>
+      <c r="H493">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494">
+        <v>28</v>
+      </c>
+      <c r="B494" s="1">
+        <v>44058.083333333336</v>
+      </c>
+      <c r="C494" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D494" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E494" t="str">
+        <v>1,17</v>
+      </c>
+      <c r="F494" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G494" t="str">
+        <v>m</v>
+      </c>
+      <c r="H494">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495">
+        <v>28</v>
+      </c>
+      <c r="B495" s="1">
+        <v>44058.083333333336</v>
+      </c>
+      <c r="C495" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D495" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E495" t="str">
+        <v>73,2</v>
+      </c>
+      <c r="F495" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G495" t="str">
+        <v>m</v>
+      </c>
+      <c r="H495">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496">
+        <v>28</v>
+      </c>
+      <c r="B496" s="1">
+        <v>44242.041666666664</v>
+      </c>
+      <c r="C496" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D496" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E496" t="str">
+        <v>1,13</v>
+      </c>
+      <c r="F496" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G496" t="str">
+        <v>m</v>
+      </c>
+      <c r="H496">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497">
+        <v>28</v>
+      </c>
+      <c r="B497" s="1">
+        <v>44242.041666666664</v>
+      </c>
+      <c r="C497" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D497" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E497" t="str">
+        <v>75,8</v>
+      </c>
+      <c r="F497" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G497" t="str">
+        <v>m</v>
+      </c>
+      <c r="H497">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498">
+        <v>28</v>
+      </c>
+      <c r="B498" s="1">
+        <v>44423.083333333336</v>
+      </c>
+      <c r="C498" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D498" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E498" t="str">
+        <v>1,17</v>
+      </c>
+      <c r="F498" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G498" t="str">
+        <v>m</v>
+      </c>
+      <c r="H498">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499">
+        <v>28</v>
+      </c>
+      <c r="B499" s="1">
+        <v>44423.083333333336</v>
+      </c>
+      <c r="C499" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D499" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E499" t="str">
+        <v>72,7</v>
+      </c>
+      <c r="F499" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G499" t="str">
+        <v>m</v>
+      </c>
+      <c r="H499">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500">
+        <v>28</v>
+      </c>
+      <c r="B500" s="1">
+        <v>44602.041666666664</v>
+      </c>
+      <c r="C500" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D500" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E500" t="str">
+        <v>1,16</v>
+      </c>
+      <c r="F500" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G500" t="str">
+        <v>m</v>
+      </c>
+      <c r="H500">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501">
+        <v>28</v>
+      </c>
+      <c r="B501" s="1">
+        <v>44602.041666666664</v>
+      </c>
+      <c r="C501" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D501" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E501" t="str">
+        <v>73,0</v>
+      </c>
+      <c r="F501" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G501" t="str">
+        <v>m</v>
+      </c>
+      <c r="H501">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502">
+        <v>28</v>
+      </c>
+      <c r="B502" s="1">
+        <v>44788.083333333336</v>
+      </c>
+      <c r="C502" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D502" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E502" t="str">
+        <v>1,23</v>
+      </c>
+      <c r="F502" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G502" t="str">
+        <v>m</v>
+      </c>
+      <c r="H502">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503">
+        <v>28</v>
+      </c>
+      <c r="B503" s="1">
+        <v>44788.083333333336</v>
+      </c>
+      <c r="C503" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D503" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E503" t="str">
+        <v>68,1</v>
+      </c>
+      <c r="F503" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G503" t="str">
+        <v>m</v>
+      </c>
+      <c r="H503">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504">
+        <v>28</v>
+      </c>
+      <c r="B504" s="1">
+        <v>44972.041666666664</v>
+      </c>
+      <c r="C504" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D504" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E504" t="str">
+        <v>1,22</v>
+      </c>
+      <c r="F504" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G504" t="str">
+        <v>m</v>
+      </c>
+      <c r="H504">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505">
+        <v>28</v>
+      </c>
+      <c r="B505" s="1">
+        <v>44972.041666666664</v>
+      </c>
+      <c r="C505" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D505" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E505" t="str">
+        <v>68,3</v>
+      </c>
+      <c r="F505" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G505" t="str">
+        <v>m</v>
+      </c>
+      <c r="H505">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506">
+        <v>28</v>
+      </c>
+      <c r="B506" s="1">
+        <v>45151.083333333336</v>
+      </c>
+      <c r="C506" t="str">
+        <v>Kreatinin</v>
+      </c>
+      <c r="D506" t="str">
+        <v>mg/dl</v>
+      </c>
+      <c r="E506" t="str">
+        <v>1,32</v>
+      </c>
+      <c r="F506" t="str">
+        <v>2160-0</v>
+      </c>
+      <c r="G506" t="str">
+        <v>m</v>
+      </c>
+      <c r="H506">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507">
+        <v>28</v>
+      </c>
+      <c r="B507" s="1">
+        <v>45151.083333333336</v>
+      </c>
+      <c r="C507" t="str">
+        <v>eGFR</v>
+      </c>
+      <c r="D507" t="str">
+        <v>ml/min/1,73m²</v>
+      </c>
+      <c r="E507" t="str">
+        <v>62,1</v>
+      </c>
+      <c r="F507" t="str">
+        <v>98979-8</v>
+      </c>
+      <c r="G507" t="str">
+        <v>m</v>
+      </c>
+      <c r="H507">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H475"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H507"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12855,7 +13687,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13201,9 +14033,37 @@
         <v>B</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26">
+        <v>27</v>
+      </c>
+      <c r="B26" t="str">
+        <v>UMOD</v>
+      </c>
+      <c r="C26" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D26" t="str">
+        <v>A</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>28</v>
+      </c>
+      <c r="B27" t="str">
+        <v>UMOD</v>
+      </c>
+      <c r="C27" t="str">
+        <v>AD</v>
+      </c>
+      <c r="D27" t="str">
+        <v>A</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D27"/>
   </ignoredErrors>
 </worksheet>
 </file>